--- a/client/public/artefactos/ADI-05.xlsx
+++ b/client/public/artefactos/ADI-05.xlsx
@@ -271,7 +271,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -455,11 +455,44 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -608,6 +641,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/client/public/artefactos/ADI-05.xlsx
+++ b/client/public/artefactos/ADI-05.xlsx
@@ -11810,7 +11810,11 @@
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>EXT_FALLECIDOS_RENIEC_20530</t>
@@ -11872,7 +11876,11 @@
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>TMP_T732_NOVEDAD</t>
@@ -11934,7 +11942,11 @@
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>CTL_CARG_ARCHIV_EXT</t>
@@ -11996,7 +12008,11 @@
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>CTL_CARG_ARCHIV_EXT</t>
@@ -12058,7 +12074,11 @@
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>CTL_CARG_ARCHIV_EXT</t>
@@ -12120,7 +12140,11 @@
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>CTL_CARG_ARCHIV_EXT</t>
@@ -12186,7 +12210,11 @@
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>CARGA</t>
@@ -12207,7 +12235,11 @@
           <t>179</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr"/>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Archivo plano (texto)</t>
+        </is>
+      </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
@@ -12232,7 +12264,11 @@
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" t="inlineStr">
         <is>
@@ -12282,7 +12318,11 @@
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr"/>
       <c r="M182" t="inlineStr">
         <is>
@@ -12336,7 +12376,11 @@
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>TMP_AUX_AREA_GEOG</t>
@@ -12402,7 +12446,11 @@
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>TMP_T3731RUCESTANE</t>
@@ -12468,7 +12516,11 @@
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>TMP_CAT_ESTD_CONT</t>
@@ -12534,7 +12586,11 @@
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>TMP_CAT_TIPO_ACTI_ECON</t>
@@ -12600,7 +12656,11 @@
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>TMP_CAT_TIPO_DOCU_IDEN</t>
@@ -12666,7 +12726,11 @@
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>TMP_CAT_TIPO_ESTB</t>
@@ -12732,7 +12796,11 @@
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>TMP_CAT_TIPO_VIA</t>
@@ -12798,7 +12866,11 @@
       </c>
       <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>TMP_CAT_TIPO_ZONA</t>
@@ -12833,7 +12905,11 @@
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
@@ -12848,7 +12924,11 @@
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr"/>
       <c r="M191" t="inlineStr"/>
       <c r="N191" t="inlineStr">
@@ -12902,7 +12982,11 @@
       </c>
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>EXT_FALLECIDOS_RENIEC_20530</t>
@@ -12964,7 +13048,11 @@
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>TMP_T732_NOVEDAD</t>
@@ -13026,7 +13114,11 @@
       </c>
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>TMP_T818_NOVEDAD</t>
@@ -13088,7 +13180,11 @@
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>L3899HISREPLEG</t>
@@ -13150,7 +13246,11 @@
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>TMP_PADRUC</t>
@@ -13216,7 +13316,11 @@
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr"/>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>T3718CABDECJUR; T3718CABDECJUR_ERROR</t>
@@ -13245,7 +13349,11 @@
           <t>196</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr"/>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr">
         <is>
@@ -13270,7 +13378,11 @@
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr"/>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>T3718CABDECJUR</t>
@@ -13336,7 +13448,11 @@
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>T3720DETDECJUR; T3720DETDECJUR_ERROR</t>
@@ -13365,7 +13481,11 @@
           <t>198</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr"/>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr">
         <is>
@@ -13390,7 +13510,11 @@
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr"/>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>T3720DETDECJUR</t>
@@ -13456,7 +13580,11 @@
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr"/>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>T9962DJCTAIND; T9962DJCTAIND_ERROR</t>
@@ -13485,7 +13613,11 @@
           <t>200</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr"/>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Archivo plano (texto)</t>
+        </is>
+      </c>
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
@@ -13514,7 +13646,11 @@
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr"/>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>T9997DOMICILIO; T9997DOMICILIO_ERROR</t>
@@ -13543,7 +13679,11 @@
           <t>201</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr"/>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Archivo plano (texto)</t>
+        </is>
+      </c>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
         <is>
@@ -13572,7 +13712,11 @@
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>T9986EMPL; T9986EMPL_ERROR</t>
@@ -13601,7 +13745,11 @@
           <t>202</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr"/>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Archivo plano (texto)</t>
+        </is>
+      </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr">
         <is>
@@ -13630,7 +13778,11 @@
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr"/>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>T9987EMPLTER; T9987EMPLTER_ERROR</t>
@@ -13659,7 +13811,11 @@
           <t>203</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr"/>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Archivo plano (texto)</t>
+        </is>
+      </c>
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr">
         <is>
@@ -13688,7 +13844,11 @@
       </c>
       <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr"/>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>T9953F1674CTAPRO; T9953F1674CTAPRO_ERROR</t>
@@ -13717,7 +13877,11 @@
           <t>204</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr"/>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Archivo plano (texto)</t>
+        </is>
+      </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
         <is>
@@ -13746,7 +13910,11 @@
       </c>
       <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr"/>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>T9954F1674RET; T9954F1674RET_ERROR</t>
@@ -13775,7 +13943,11 @@
           <t>205</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr"/>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Archivo plano (texto)</t>
+        </is>
+      </c>
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
@@ -13804,7 +13976,11 @@
       </c>
       <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr"/>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>T3723FORREN; T3723FORREN_ERROR</t>
@@ -13833,7 +14009,11 @@
           <t>206</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr"/>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Archivo plano (texto)</t>
+        </is>
+      </c>
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
@@ -13862,7 +14042,11 @@
       </c>
       <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr"/>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>T9991IDE_ALT; T9991IDE_ALT_ERROR</t>
@@ -13928,7 +14112,11 @@
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr"/>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>T10064INGDESAPO; T10064INGDESAPO_ERROR</t>
@@ -13994,7 +14182,11 @@
       </c>
       <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr"/>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>T9964JORLAB; T9964JORLAB_ERROR</t>
@@ -14023,7 +14215,11 @@
           <t>209</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr"/>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
         <is>
@@ -14048,7 +14244,11 @@
       <c r="H211" t="inlineStr"/>
       <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr"/>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>T9964JORLAB</t>
@@ -14077,7 +14277,11 @@
           <t>210</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr"/>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Archivo plano (texto)</t>
+        </is>
+      </c>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
@@ -14106,7 +14310,11 @@
       </c>
       <c r="I212" t="inlineStr"/>
       <c r="J212" t="inlineStr"/>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>T9988LOCEMPL; T9988LOCEMPL_ERROR</t>
@@ -14135,7 +14343,11 @@
           <t>211</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr"/>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Archivo plano (texto)</t>
+        </is>
+      </c>
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
@@ -14164,7 +14376,11 @@
       </c>
       <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr"/>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>T9995LOCPRE; T9995LOCPRE_ERROR</t>
@@ -14193,7 +14409,11 @@
           <t>212</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr"/>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Archivo plano (texto)</t>
+        </is>
+      </c>
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
@@ -14222,7 +14442,11 @@
       </c>
       <c r="I214" t="inlineStr"/>
       <c r="J214" t="inlineStr"/>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>T2101NOTAABO; T2101NOTAABO_ERROR</t>
@@ -14284,7 +14508,11 @@
       <c r="H215" t="inlineStr"/>
       <c r="I215" t="inlineStr"/>
       <c r="J215" t="inlineStr"/>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>P2059FORMUL; P2059FORMUL_ERROR</t>
@@ -14305,7 +14533,11 @@
           <t>214</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr"/>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Archivo plano (texto)</t>
+        </is>
+      </c>
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
         <is>
@@ -14334,7 +14566,11 @@
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr"/>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>T10152PADREIMP; T10152PADREIMP_ERROR</t>
@@ -14400,7 +14636,11 @@
       </c>
       <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr"/>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>T10011PUBIGEORENIEC; T10012PPAIS; T10014PNACION; T10015CATPRE; T10016PTIPPRES; T10017PREGIMEN; T10019PMOTBAJREG; t10010pliegopre; t10013pcodldn</t>
@@ -14466,7 +14706,11 @@
       </c>
       <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr"/>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>P2035BANCO; T3721ENTBEN; T3722FACCOP; T9970TIPSUSP</t>
@@ -14495,7 +14739,11 @@
           <t>217</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr"/>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Archivo plano (texto)</t>
+        </is>
+      </c>
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
         <is>
@@ -14524,7 +14772,11 @@
       </c>
       <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr"/>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>T9937PADDEVOL; T9937PADDEVOL_ERROR</t>
@@ -14553,7 +14805,11 @@
           <t>218</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr"/>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Archivo plano (texto)</t>
+        </is>
+      </c>
       <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
@@ -14582,7 +14838,11 @@
       </c>
       <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr"/>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>T9993PERLAB; T9993PERLAB_ERROR</t>
@@ -14611,7 +14871,11 @@
           <t>219</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr"/>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Archivo plano (texto)</t>
+        </is>
+      </c>
       <c r="C221" t="inlineStr"/>
       <c r="D221" t="inlineStr">
         <is>
@@ -14640,7 +14904,11 @@
       </c>
       <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr"/>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>T9989PERSONA; T9989PERSONA_ERROR</t>
@@ -14669,7 +14937,11 @@
           <t>220</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr"/>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Archivo plano (texto)</t>
+        </is>
+      </c>
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr">
         <is>
@@ -14698,7 +14970,11 @@
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr"/>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>T9996REG_PREST; T9996REG_PREST_ERROR</t>
@@ -14727,7 +15003,11 @@
           <t>221</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr"/>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Archivo plano (texto)</t>
+        </is>
+      </c>
       <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr">
         <is>
@@ -14756,7 +15036,11 @@
       </c>
       <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr"/>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>T9994PRESTADOR; T9994PRESTADOR_ERROR</t>
@@ -14785,7 +15069,11 @@
           <t>222</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr"/>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Archivo plano (texto)</t>
+        </is>
+      </c>
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr">
         <is>
@@ -14814,7 +15102,11 @@
       </c>
       <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr"/>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>T3707RECFECFOR; T3707RECFECFOR_ERROR</t>
@@ -14843,7 +15135,11 @@
           <t>223</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr"/>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Archivo plano (texto)</t>
+        </is>
+      </c>
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr">
         <is>
@@ -14872,7 +15168,11 @@
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr"/>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>T3705RECNABENT; T3705RECNABENT_ERROR</t>
@@ -14901,7 +15201,11 @@
           <t>224</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr"/>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Archivo plano (texto)</t>
+        </is>
+      </c>
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr">
         <is>
@@ -14930,7 +15234,11 @@
       </c>
       <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr"/>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>T9990IDE_RENIEC; T9990IDE_RENIEC_ERROR</t>
@@ -14996,7 +15304,11 @@
       </c>
       <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr"/>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>T10063SEMCON; T10063SEMCON_ERROR</t>
@@ -15062,7 +15374,11 @@
       </c>
       <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>T9966SUSPLABOR; T9966SUSPLABOR_ERROR</t>
@@ -15128,7 +15444,11 @@
       </c>
       <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr"/>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>T3704CASILLAS; T3704CASILLAS_ERROR</t>
@@ -15186,7 +15506,11 @@
       </c>
       <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr"/>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>T3708CASTRI; T3708CASTRI_ERROR</t>
@@ -15244,7 +15568,11 @@
       </c>
       <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr"/>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>T3711CASPAG; T3711CASPAG_ERROR</t>
@@ -15265,7 +15593,11 @@
           <t>230</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr"/>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Archivo plano (texto)</t>
+        </is>
+      </c>
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr">
         <is>
@@ -15294,7 +15626,11 @@
       </c>
       <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr"/>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>T9992VINLAB; T9992VINLAB_ERROR</t>
@@ -15356,7 +15692,11 @@
       </c>
       <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr"/>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>Tmp_T3493_Novedad_aux; Tmp_novedad_parametro_3493</t>
@@ -15418,7 +15758,11 @@
       </c>
       <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr"/>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>TMP_NOVE_CORR</t>
@@ -15453,7 +15797,11 @@
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
@@ -15468,7 +15816,11 @@
       <c r="H235" t="inlineStr"/>
       <c r="I235" t="inlineStr"/>
       <c r="J235" t="inlineStr"/>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr"/>
       <c r="M235" t="inlineStr"/>
       <c r="N235" t="inlineStr">
@@ -15522,7 +15874,11 @@
       </c>
       <c r="I236" t="inlineStr"/>
       <c r="J236" t="inlineStr"/>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>Tmp_T727_Novedad_aux_prev; Tmp_novedad_parametro; ora_tmp_onp_pag_nov</t>
@@ -15584,7 +15940,11 @@
       </c>
       <c r="I237" t="inlineStr"/>
       <c r="J237" t="inlineStr"/>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>TMP_T732_NOVEDAD_AUX</t>
@@ -15646,7 +16006,11 @@
       </c>
       <c r="I238" t="inlineStr"/>
       <c r="J238" t="inlineStr"/>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>TMP_T733_NOVEDAD_AUX</t>
@@ -15708,7 +16072,11 @@
       </c>
       <c r="I239" t="inlineStr"/>
       <c r="J239" t="inlineStr"/>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>TMP_NULIDAD</t>
@@ -15770,7 +16138,11 @@
       </c>
       <c r="I240" t="inlineStr"/>
       <c r="J240" t="inlineStr"/>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>p2003tipdocide</t>
@@ -15832,7 +16204,11 @@
       </c>
       <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr"/>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>P2008ESTCONTRI</t>
@@ -15894,7 +16270,11 @@
       </c>
       <c r="I242" t="inlineStr"/>
       <c r="J242" t="inlineStr"/>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>P2011TIPCONTRI</t>
@@ -15956,7 +16336,11 @@
       </c>
       <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr"/>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>P2014DEPEN</t>
@@ -16018,7 +16402,11 @@
       </c>
       <c r="I244" t="inlineStr"/>
       <c r="J244" t="inlineStr"/>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>P2025TIPVIA</t>
@@ -16080,7 +16468,11 @@
       </c>
       <c r="I245" t="inlineStr"/>
       <c r="J245" t="inlineStr"/>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>P2029TIPZON</t>
@@ -16142,7 +16534,11 @@
       </c>
       <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr"/>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>P2030UBIGEO</t>
@@ -16204,7 +16600,11 @@
       </c>
       <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr"/>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>P2032TRIBUTOS</t>
@@ -16266,7 +16666,11 @@
       </c>
       <c r="I248" t="inlineStr"/>
       <c r="J248" t="inlineStr"/>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>P2052TIPCARGO</t>
@@ -16328,7 +16732,11 @@
       </c>
       <c r="I249" t="inlineStr"/>
       <c r="J249" t="inlineStr"/>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>p2129tipestab</t>
@@ -16390,7 +16798,11 @@
       </c>
       <c r="I250" t="inlineStr"/>
       <c r="J250" t="inlineStr"/>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>P2008ESTCONTRI</t>
@@ -16452,7 +16864,11 @@
       </c>
       <c r="I251" t="inlineStr"/>
       <c r="J251" t="inlineStr"/>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>TMP_PADRON</t>
@@ -16514,7 +16930,11 @@
       </c>
       <c r="I252" t="inlineStr"/>
       <c r="J252" t="inlineStr"/>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>TMP_PADRON_AFP</t>
@@ -16580,7 +17000,11 @@
       </c>
       <c r="I253" t="inlineStr"/>
       <c r="J253" t="inlineStr"/>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>TMP_T3730REGRUCCIIU</t>
@@ -16642,7 +17066,11 @@
       </c>
       <c r="I254" t="inlineStr"/>
       <c r="J254" t="inlineStr"/>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>TMP_RELACION_LABORAL</t>
@@ -16671,7 +17099,11 @@
           <t>253</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr"/>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C255" t="inlineStr"/>
       <c r="D255" t="inlineStr">
         <is>
@@ -16700,7 +17132,11 @@
       </c>
       <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr"/>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>T3718CABDECJUR</t>
@@ -16729,7 +17165,11 @@
           <t>254</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr"/>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C256" t="inlineStr"/>
       <c r="D256" t="inlineStr">
         <is>
@@ -16758,7 +17198,11 @@
       </c>
       <c r="I256" t="inlineStr"/>
       <c r="J256" t="inlineStr"/>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>T3720DETDECJUR</t>
@@ -16787,7 +17231,11 @@
           <t>255</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr"/>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C257" t="inlineStr"/>
       <c r="D257" t="inlineStr">
         <is>
@@ -16816,7 +17264,11 @@
       </c>
       <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr"/>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>T9962DJCTAIND</t>
@@ -16845,7 +17297,11 @@
           <t>256</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr"/>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C258" t="inlineStr"/>
       <c r="D258" t="inlineStr">
         <is>
@@ -16874,7 +17330,11 @@
       </c>
       <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr"/>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>T9997DOMICILIO</t>
@@ -16903,7 +17363,11 @@
           <t>257</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr"/>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C259" t="inlineStr"/>
       <c r="D259" t="inlineStr">
         <is>
@@ -16932,7 +17396,11 @@
       </c>
       <c r="I259" t="inlineStr"/>
       <c r="J259" t="inlineStr"/>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>T9986EMPL</t>
@@ -16961,7 +17429,11 @@
           <t>258</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr"/>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C260" t="inlineStr"/>
       <c r="D260" t="inlineStr">
         <is>
@@ -16990,7 +17462,11 @@
       </c>
       <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr"/>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>T9987EMPLTER</t>
@@ -17019,7 +17495,11 @@
           <t>259</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr"/>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C261" t="inlineStr"/>
       <c r="D261" t="inlineStr">
         <is>
@@ -17048,7 +17528,11 @@
       </c>
       <c r="I261" t="inlineStr"/>
       <c r="J261" t="inlineStr"/>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>T9953F1674CTAPRO</t>
@@ -17077,7 +17561,11 @@
           <t>260</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr"/>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C262" t="inlineStr"/>
       <c r="D262" t="inlineStr">
         <is>
@@ -17106,7 +17594,11 @@
       </c>
       <c r="I262" t="inlineStr"/>
       <c r="J262" t="inlineStr"/>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>T9954F1674RET</t>
@@ -17135,7 +17627,11 @@
           <t>261</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr"/>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C263" t="inlineStr"/>
       <c r="D263" t="inlineStr">
         <is>
@@ -17164,7 +17660,11 @@
       </c>
       <c r="I263" t="inlineStr"/>
       <c r="J263" t="inlineStr"/>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>T3723FORREN</t>
@@ -17226,7 +17726,11 @@
       </c>
       <c r="I264" t="inlineStr"/>
       <c r="J264" t="inlineStr"/>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>T10041HCABDECJUR</t>
@@ -17288,7 +17792,11 @@
       </c>
       <c r="I265" t="inlineStr"/>
       <c r="J265" t="inlineStr"/>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>T10042HDETDECJUR</t>
@@ -17317,7 +17825,11 @@
           <t>264</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr"/>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr">
         <is>
@@ -17346,7 +17858,11 @@
       </c>
       <c r="I266" t="inlineStr"/>
       <c r="J266" t="inlineStr"/>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>T9963HDJCTAIND</t>
@@ -17375,7 +17891,11 @@
           <t>265</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr"/>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C267" t="inlineStr"/>
       <c r="D267" t="inlineStr">
         <is>
@@ -17404,7 +17924,11 @@
       </c>
       <c r="I267" t="inlineStr"/>
       <c r="J267" t="inlineStr"/>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>T10009HDOMICILIO</t>
@@ -17433,7 +17957,11 @@
           <t>266</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr"/>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C268" t="inlineStr"/>
       <c r="D268" t="inlineStr">
         <is>
@@ -17462,7 +17990,11 @@
       </c>
       <c r="I268" t="inlineStr"/>
       <c r="J268" t="inlineStr"/>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>T9998HEMPL</t>
@@ -17524,7 +18056,11 @@
       </c>
       <c r="I269" t="inlineStr"/>
       <c r="J269" t="inlineStr"/>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>T9999HEMPLTER</t>
@@ -17553,7 +18089,11 @@
           <t>268</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr"/>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr">
         <is>
@@ -17582,7 +18122,11 @@
       </c>
       <c r="I270" t="inlineStr"/>
       <c r="J270" t="inlineStr"/>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>T10003HIDE_ALT</t>
@@ -17611,7 +18155,11 @@
           <t>269</t>
         </is>
       </c>
-      <c r="B271" t="inlineStr"/>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C271" t="inlineStr"/>
       <c r="D271" t="inlineStr">
         <is>
@@ -17640,7 +18188,11 @@
       </c>
       <c r="I271" t="inlineStr"/>
       <c r="J271" t="inlineStr"/>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>T10002HIDE_RENIEC</t>
@@ -17669,7 +18221,11 @@
           <t>270</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr"/>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr">
         <is>
@@ -17698,7 +18254,11 @@
       </c>
       <c r="I272" t="inlineStr"/>
       <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>T10066HINGDESAPO</t>
@@ -17727,7 +18287,11 @@
           <t>271</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr"/>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr">
         <is>
@@ -17756,7 +18320,11 @@
       </c>
       <c r="I273" t="inlineStr"/>
       <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>T9965HJORLAB</t>
@@ -17785,7 +18353,11 @@
           <t>272</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr"/>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr">
         <is>
@@ -17814,7 +18386,11 @@
       </c>
       <c r="I274" t="inlineStr"/>
       <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>T10000HLOCEMPL</t>
@@ -17843,7 +18419,11 @@
           <t>273</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr"/>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr">
         <is>
@@ -17872,7 +18452,11 @@
       </c>
       <c r="I275" t="inlineStr"/>
       <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>T10008HLOCPRE</t>
@@ -17926,7 +18510,11 @@
       </c>
       <c r="I276" t="inlineStr"/>
       <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>T10153HPADREIMP</t>
@@ -17988,7 +18576,11 @@
       </c>
       <c r="I277" t="inlineStr"/>
       <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>T10005HPERLAB</t>
@@ -18017,7 +18609,11 @@
           <t>276</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr"/>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr">
         <is>
@@ -18046,7 +18642,11 @@
       </c>
       <c r="I278" t="inlineStr"/>
       <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>T10001HPERSONA</t>
@@ -18075,7 +18675,11 @@
           <t>277</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr"/>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr">
         <is>
@@ -18104,7 +18708,11 @@
       </c>
       <c r="I279" t="inlineStr"/>
       <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>T10006HPRESTADOR</t>
@@ -18133,7 +18741,11 @@
           <t>278</t>
         </is>
       </c>
-      <c r="B280" t="inlineStr"/>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr">
         <is>
@@ -18162,7 +18774,11 @@
       </c>
       <c r="I280" t="inlineStr"/>
       <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>T10007HREG_PREST</t>
@@ -18183,7 +18799,11 @@
           <t>279</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr"/>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C281" t="inlineStr"/>
       <c r="D281" t="inlineStr">
         <is>
@@ -18212,7 +18832,11 @@
       </c>
       <c r="I281" t="inlineStr"/>
       <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>T10065HSEMCON</t>
@@ -18241,7 +18865,11 @@
           <t>280</t>
         </is>
       </c>
-      <c r="B282" t="inlineStr"/>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C282" t="inlineStr"/>
       <c r="D282" t="inlineStr">
         <is>
@@ -18270,7 +18898,11 @@
       </c>
       <c r="I282" t="inlineStr"/>
       <c r="J282" t="inlineStr"/>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>T9967HSUSPLABOR</t>
@@ -18332,7 +18964,11 @@
       </c>
       <c r="I283" t="inlineStr"/>
       <c r="J283" t="inlineStr"/>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>T10004HVINLAB</t>
@@ -18361,7 +18997,11 @@
           <t>282</t>
         </is>
       </c>
-      <c r="B284" t="inlineStr"/>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C284" t="inlineStr"/>
       <c r="D284" t="inlineStr">
         <is>
@@ -18390,7 +19030,11 @@
       </c>
       <c r="I284" t="inlineStr"/>
       <c r="J284" t="inlineStr"/>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>T9991IDE_ALT</t>
@@ -18419,7 +19063,11 @@
           <t>283</t>
         </is>
       </c>
-      <c r="B285" t="inlineStr"/>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C285" t="inlineStr"/>
       <c r="D285" t="inlineStr">
         <is>
@@ -18448,7 +19096,11 @@
       </c>
       <c r="I285" t="inlineStr"/>
       <c r="J285" t="inlineStr"/>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>T10064INGDESAPO</t>
@@ -18477,7 +19129,11 @@
           <t>284</t>
         </is>
       </c>
-      <c r="B286" t="inlineStr"/>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr">
         <is>
@@ -18506,7 +19162,11 @@
       </c>
       <c r="I286" t="inlineStr"/>
       <c r="J286" t="inlineStr"/>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>T9964JORLAB</t>
@@ -18535,7 +19195,11 @@
           <t>285</t>
         </is>
       </c>
-      <c r="B287" t="inlineStr"/>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C287" t="inlineStr"/>
       <c r="D287" t="inlineStr">
         <is>
@@ -18564,7 +19228,11 @@
       </c>
       <c r="I287" t="inlineStr"/>
       <c r="J287" t="inlineStr"/>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>T9988LOCEMPL</t>
@@ -18593,7 +19261,11 @@
           <t>286</t>
         </is>
       </c>
-      <c r="B288" t="inlineStr"/>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C288" t="inlineStr"/>
       <c r="D288" t="inlineStr">
         <is>
@@ -18622,7 +19294,11 @@
       </c>
       <c r="I288" t="inlineStr"/>
       <c r="J288" t="inlineStr"/>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>T9995LOCPRE</t>
@@ -18651,7 +19327,11 @@
           <t>287</t>
         </is>
       </c>
-      <c r="B289" t="inlineStr"/>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C289" t="inlineStr"/>
       <c r="D289" t="inlineStr">
         <is>
@@ -18680,7 +19360,11 @@
       </c>
       <c r="I289" t="inlineStr"/>
       <c r="J289" t="inlineStr"/>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>T2101NOTAABO</t>
@@ -18709,7 +19393,11 @@
           <t>288</t>
         </is>
       </c>
-      <c r="B290" t="inlineStr"/>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C290" t="inlineStr"/>
       <c r="D290" t="inlineStr">
         <is>
@@ -18738,7 +19426,11 @@
       </c>
       <c r="I290" t="inlineStr"/>
       <c r="J290" t="inlineStr"/>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>T10152PADREIMP</t>
@@ -18767,7 +19459,11 @@
           <t>289</t>
         </is>
       </c>
-      <c r="B291" t="inlineStr"/>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C291" t="inlineStr"/>
       <c r="D291" t="inlineStr">
         <is>
@@ -18796,7 +19492,11 @@
       </c>
       <c r="I291" t="inlineStr"/>
       <c r="J291" t="inlineStr"/>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>T10011PUBIGEORENIEC; T10012PPAIS; T10014PNACION; T10015CATPRE; T10016PTIPPRES; T10017PREGIMEN; T10019PMOTBAJREG; t10010pliegopre; t10013pcodldn</t>
@@ -18825,7 +19525,11 @@
           <t>290</t>
         </is>
       </c>
-      <c r="B292" t="inlineStr"/>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C292" t="inlineStr"/>
       <c r="D292" t="inlineStr">
         <is>
@@ -18854,7 +19558,11 @@
       </c>
       <c r="I292" t="inlineStr"/>
       <c r="J292" t="inlineStr"/>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>P2035BANCO; P2059FORMUL; T3704CASILLAS; T3708CASTRI; T3711CASPAG; T3721ENTBEN; T3722FACCOP; T9970TIPSUSP</t>
@@ -18916,7 +19624,11 @@
       </c>
       <c r="I293" t="inlineStr"/>
       <c r="J293" t="inlineStr"/>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>T9937PADDEVOL</t>
@@ -18945,7 +19657,11 @@
           <t>292</t>
         </is>
       </c>
-      <c r="B294" t="inlineStr"/>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C294" t="inlineStr"/>
       <c r="D294" t="inlineStr">
         <is>
@@ -18974,7 +19690,11 @@
       </c>
       <c r="I294" t="inlineStr"/>
       <c r="J294" t="inlineStr"/>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>T9993PERLAB</t>
@@ -19003,7 +19723,11 @@
           <t>293</t>
         </is>
       </c>
-      <c r="B295" t="inlineStr"/>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C295" t="inlineStr"/>
       <c r="D295" t="inlineStr">
         <is>
@@ -19032,7 +19756,11 @@
       </c>
       <c r="I295" t="inlineStr"/>
       <c r="J295" t="inlineStr"/>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>T9989PERSONA</t>
@@ -19061,7 +19789,11 @@
           <t>294</t>
         </is>
       </c>
-      <c r="B296" t="inlineStr"/>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C296" t="inlineStr"/>
       <c r="D296" t="inlineStr">
         <is>
@@ -19090,7 +19822,11 @@
       </c>
       <c r="I296" t="inlineStr"/>
       <c r="J296" t="inlineStr"/>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>T9996REG_PREST</t>
@@ -19119,7 +19855,11 @@
           <t>295</t>
         </is>
       </c>
-      <c r="B297" t="inlineStr"/>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C297" t="inlineStr"/>
       <c r="D297" t="inlineStr">
         <is>
@@ -19148,7 +19888,11 @@
       </c>
       <c r="I297" t="inlineStr"/>
       <c r="J297" t="inlineStr"/>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>T9994PRESTADOR</t>
@@ -19177,7 +19921,11 @@
           <t>296</t>
         </is>
       </c>
-      <c r="B298" t="inlineStr"/>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C298" t="inlineStr"/>
       <c r="D298" t="inlineStr">
         <is>
@@ -19206,7 +19954,11 @@
       </c>
       <c r="I298" t="inlineStr"/>
       <c r="J298" t="inlineStr"/>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>T3707RECFECFOR</t>
@@ -19235,7 +19987,11 @@
           <t>297</t>
         </is>
       </c>
-      <c r="B299" t="inlineStr"/>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C299" t="inlineStr"/>
       <c r="D299" t="inlineStr">
         <is>
@@ -19264,7 +20020,11 @@
       </c>
       <c r="I299" t="inlineStr"/>
       <c r="J299" t="inlineStr"/>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>T3705RECNABENT</t>
@@ -19293,7 +20053,11 @@
           <t>298</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr"/>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C300" t="inlineStr"/>
       <c r="D300" t="inlineStr">
         <is>
@@ -19322,7 +20086,11 @@
       </c>
       <c r="I300" t="inlineStr"/>
       <c r="J300" t="inlineStr"/>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>T9990IDE_RENIEC</t>
@@ -19351,7 +20119,11 @@
           <t>299</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr"/>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C301" t="inlineStr"/>
       <c r="D301" t="inlineStr">
         <is>
@@ -19380,7 +20152,11 @@
       </c>
       <c r="I301" t="inlineStr"/>
       <c r="J301" t="inlineStr"/>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>T10063SEMCON</t>
@@ -19409,7 +20185,11 @@
           <t>300</t>
         </is>
       </c>
-      <c r="B302" t="inlineStr"/>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr">
         <is>
@@ -19438,7 +20218,11 @@
       </c>
       <c r="I302" t="inlineStr"/>
       <c r="J302" t="inlineStr"/>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>T9966SUSPLABOR</t>
@@ -19496,7 +20280,11 @@
       <c r="H303" t="inlineStr"/>
       <c r="I303" t="inlineStr"/>
       <c r="J303" t="inlineStr"/>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr"/>
       <c r="M303" t="inlineStr"/>
       <c r="N303" t="inlineStr"/>
@@ -19538,7 +20326,11 @@
       <c r="H304" t="inlineStr"/>
       <c r="I304" t="inlineStr"/>
       <c r="J304" t="inlineStr"/>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr"/>
       <c r="M304" t="inlineStr"/>
       <c r="N304" t="inlineStr"/>
@@ -19580,7 +20372,11 @@
       <c r="H305" t="inlineStr"/>
       <c r="I305" t="inlineStr"/>
       <c r="J305" t="inlineStr"/>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr"/>
       <c r="M305" t="inlineStr"/>
       <c r="N305" t="inlineStr"/>
@@ -19622,7 +20418,11 @@
       <c r="H306" t="inlineStr"/>
       <c r="I306" t="inlineStr"/>
       <c r="J306" t="inlineStr"/>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr"/>
       <c r="M306" t="inlineStr"/>
       <c r="N306" t="inlineStr"/>
@@ -19664,7 +20464,11 @@
       <c r="H307" t="inlineStr"/>
       <c r="I307" t="inlineStr"/>
       <c r="J307" t="inlineStr"/>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr"/>
       <c r="M307" t="inlineStr"/>
       <c r="N307" t="inlineStr"/>
@@ -19706,7 +20510,11 @@
       <c r="H308" t="inlineStr"/>
       <c r="I308" t="inlineStr"/>
       <c r="J308" t="inlineStr"/>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr"/>
       <c r="M308" t="inlineStr"/>
       <c r="N308" t="inlineStr"/>
@@ -19748,7 +20556,11 @@
       <c r="H309" t="inlineStr"/>
       <c r="I309" t="inlineStr"/>
       <c r="J309" t="inlineStr"/>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr"/>
       <c r="M309" t="inlineStr"/>
       <c r="N309" t="inlineStr"/>
@@ -19790,7 +20602,11 @@
       <c r="H310" t="inlineStr"/>
       <c r="I310" t="inlineStr"/>
       <c r="J310" t="inlineStr"/>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr"/>
       <c r="M310" t="inlineStr"/>
       <c r="N310" t="inlineStr"/>
@@ -19832,7 +20648,11 @@
       <c r="H311" t="inlineStr"/>
       <c r="I311" t="inlineStr"/>
       <c r="J311" t="inlineStr"/>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr"/>
       <c r="M311" t="inlineStr"/>
       <c r="N311" t="inlineStr"/>
@@ -19874,7 +20694,11 @@
       <c r="H312" t="inlineStr"/>
       <c r="I312" t="inlineStr"/>
       <c r="J312" t="inlineStr"/>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr"/>
       <c r="M312" t="inlineStr"/>
       <c r="N312" t="inlineStr"/>
@@ -19916,7 +20740,11 @@
       <c r="H313" t="inlineStr"/>
       <c r="I313" t="inlineStr"/>
       <c r="J313" t="inlineStr"/>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr"/>
       <c r="M313" t="inlineStr"/>
       <c r="N313" t="inlineStr"/>
@@ -19958,7 +20786,11 @@
       <c r="H314" t="inlineStr"/>
       <c r="I314" t="inlineStr"/>
       <c r="J314" t="inlineStr"/>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr"/>
       <c r="M314" t="inlineStr"/>
       <c r="N314" t="inlineStr"/>
@@ -20000,7 +20832,11 @@
       <c r="H315" t="inlineStr"/>
       <c r="I315" t="inlineStr"/>
       <c r="J315" t="inlineStr"/>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr"/>
       <c r="M315" t="inlineStr"/>
       <c r="N315" t="inlineStr"/>
@@ -20042,7 +20878,11 @@
       <c r="H316" t="inlineStr"/>
       <c r="I316" t="inlineStr"/>
       <c r="J316" t="inlineStr"/>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr"/>
       <c r="M316" t="inlineStr"/>
       <c r="N316" t="inlineStr"/>
@@ -20084,7 +20924,11 @@
       <c r="H317" t="inlineStr"/>
       <c r="I317" t="inlineStr"/>
       <c r="J317" t="inlineStr"/>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr"/>
       <c r="M317" t="inlineStr"/>
       <c r="N317" t="inlineStr">
@@ -20134,7 +20978,11 @@
       <c r="H318" t="inlineStr"/>
       <c r="I318" t="inlineStr"/>
       <c r="J318" t="inlineStr"/>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr"/>
       <c r="M318" t="inlineStr"/>
       <c r="N318" t="inlineStr"/>
@@ -20176,7 +21024,11 @@
       <c r="H319" t="inlineStr"/>
       <c r="I319" t="inlineStr"/>
       <c r="J319" t="inlineStr"/>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr"/>
       <c r="M319" t="inlineStr"/>
       <c r="N319" t="inlineStr"/>
@@ -20218,7 +21070,11 @@
       <c r="H320" t="inlineStr"/>
       <c r="I320" t="inlineStr"/>
       <c r="J320" t="inlineStr"/>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr"/>
       <c r="M320" t="inlineStr"/>
       <c r="N320" t="inlineStr"/>
@@ -20260,7 +21116,11 @@
       <c r="H321" t="inlineStr"/>
       <c r="I321" t="inlineStr"/>
       <c r="J321" t="inlineStr"/>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr"/>
       <c r="M321" t="inlineStr"/>
       <c r="N321" t="inlineStr"/>
@@ -20302,7 +21162,11 @@
       <c r="H322" t="inlineStr"/>
       <c r="I322" t="inlineStr"/>
       <c r="J322" t="inlineStr"/>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr"/>
       <c r="M322" t="inlineStr"/>
       <c r="N322" t="inlineStr"/>
@@ -20315,7 +21179,11 @@
           <t>321</t>
         </is>
       </c>
-      <c r="B323" t="inlineStr"/>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C323" t="inlineStr"/>
       <c r="D323" t="inlineStr">
         <is>
@@ -20344,7 +21212,11 @@
       </c>
       <c r="I323" t="inlineStr"/>
       <c r="J323" t="inlineStr"/>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>T9992VINLAB</t>
@@ -20406,7 +21278,11 @@
       </c>
       <c r="I324" t="inlineStr"/>
       <c r="J324" t="inlineStr"/>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>TMP_PADRUC_EMPL_V1</t>
@@ -20468,7 +21344,11 @@
       </c>
       <c r="I325" t="inlineStr"/>
       <c r="J325" t="inlineStr"/>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>T3709RUCPERNAT</t>
@@ -20530,7 +21410,11 @@
       </c>
       <c r="I326" t="inlineStr"/>
       <c r="J326" t="inlineStr"/>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>T3712RUCREPLEG</t>
@@ -20592,7 +21476,11 @@
       </c>
       <c r="I327" t="inlineStr"/>
       <c r="J327" t="inlineStr"/>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>T3724HISPADRUC</t>
@@ -20654,7 +21542,11 @@
       </c>
       <c r="I328" t="inlineStr"/>
       <c r="J328" t="inlineStr"/>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>T3725HISVFP</t>
@@ -20716,7 +21608,11 @@
       </c>
       <c r="I329" t="inlineStr"/>
       <c r="J329" t="inlineStr"/>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>T3726PADRUC</t>
@@ -20778,7 +21674,11 @@
       </c>
       <c r="I330" t="inlineStr"/>
       <c r="J330" t="inlineStr"/>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>T3727PERREN</t>
@@ -20840,7 +21740,11 @@
       </c>
       <c r="I331" t="inlineStr"/>
       <c r="J331" t="inlineStr"/>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>T3730REGRUCCIIU</t>
@@ -20902,7 +21806,11 @@
       </c>
       <c r="I332" t="inlineStr"/>
       <c r="J332" t="inlineStr"/>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>T3731RUCESTANE</t>
@@ -20964,7 +21872,11 @@
       </c>
       <c r="I333" t="inlineStr"/>
       <c r="J333" t="inlineStr"/>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>T3735VFP</t>
@@ -21026,7 +21938,11 @@
       </c>
       <c r="I334" t="inlineStr"/>
       <c r="J334" t="inlineStr"/>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>T5465HISESTANE</t>
@@ -21065,7 +21981,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr"/>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E335" t="inlineStr"/>
       <c r="F335" t="inlineStr">
         <is>
@@ -21080,7 +22000,11 @@
       <c r="H335" t="inlineStr"/>
       <c r="I335" t="inlineStr"/>
       <c r="J335" t="inlineStr"/>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr"/>
       <c r="M335" t="inlineStr"/>
       <c r="N335" t="inlineStr">
@@ -21107,7 +22031,11 @@
         </is>
       </c>
       <c r="C336" t="inlineStr"/>
-      <c r="D336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E336" t="inlineStr"/>
       <c r="F336" t="inlineStr">
         <is>
@@ -21122,7 +22050,11 @@
       <c r="H336" t="inlineStr"/>
       <c r="I336" t="inlineStr"/>
       <c r="J336" t="inlineStr"/>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr"/>
       <c r="M336" t="inlineStr"/>
       <c r="N336" t="inlineStr">
@@ -21149,7 +22081,11 @@
         </is>
       </c>
       <c r="C337" t="inlineStr"/>
-      <c r="D337" t="inlineStr"/>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E337" t="inlineStr"/>
       <c r="F337" t="inlineStr">
         <is>
@@ -21164,7 +22100,11 @@
       <c r="H337" t="inlineStr"/>
       <c r="I337" t="inlineStr"/>
       <c r="J337" t="inlineStr"/>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr"/>
       <c r="M337" t="inlineStr"/>
       <c r="N337" t="inlineStr">
@@ -21191,7 +22131,11 @@
         </is>
       </c>
       <c r="C338" t="inlineStr"/>
-      <c r="D338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="inlineStr">
         <is>
@@ -21206,7 +22150,11 @@
       <c r="H338" t="inlineStr"/>
       <c r="I338" t="inlineStr"/>
       <c r="J338" t="inlineStr"/>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr"/>
       <c r="M338" t="inlineStr"/>
       <c r="N338" t="inlineStr">
@@ -21233,7 +22181,11 @@
         </is>
       </c>
       <c r="C339" t="inlineStr"/>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr"/>
       <c r="F339" t="inlineStr">
         <is>
@@ -21248,7 +22200,11 @@
       <c r="H339" t="inlineStr"/>
       <c r="I339" t="inlineStr"/>
       <c r="J339" t="inlineStr"/>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr"/>
       <c r="M339" t="inlineStr"/>
       <c r="N339" t="inlineStr">
@@ -21275,7 +22231,11 @@
         </is>
       </c>
       <c r="C340" t="inlineStr"/>
-      <c r="D340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr"/>
       <c r="F340" t="inlineStr">
         <is>
@@ -21290,7 +22250,11 @@
       <c r="H340" t="inlineStr"/>
       <c r="I340" t="inlineStr"/>
       <c r="J340" t="inlineStr"/>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr"/>
       <c r="M340" t="inlineStr"/>
       <c r="N340" t="inlineStr">
@@ -21317,7 +22281,11 @@
         </is>
       </c>
       <c r="C341" t="inlineStr"/>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr"/>
       <c r="F341" t="inlineStr">
         <is>
@@ -21332,7 +22300,11 @@
       <c r="H341" t="inlineStr"/>
       <c r="I341" t="inlineStr"/>
       <c r="J341" t="inlineStr"/>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr"/>
       <c r="M341" t="inlineStr"/>
       <c r="N341" t="inlineStr">
@@ -21359,7 +22331,11 @@
         </is>
       </c>
       <c r="C342" t="inlineStr"/>
-      <c r="D342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr"/>
       <c r="F342" t="inlineStr">
         <is>
@@ -21374,7 +22350,11 @@
       <c r="H342" t="inlineStr"/>
       <c r="I342" t="inlineStr"/>
       <c r="J342" t="inlineStr"/>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr"/>
       <c r="M342" t="inlineStr"/>
       <c r="N342" t="inlineStr">
@@ -21401,7 +22381,11 @@
         </is>
       </c>
       <c r="C343" t="inlineStr"/>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr"/>
       <c r="F343" t="inlineStr">
         <is>
@@ -21416,7 +22400,11 @@
       <c r="H343" t="inlineStr"/>
       <c r="I343" t="inlineStr"/>
       <c r="J343" t="inlineStr"/>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr"/>
       <c r="M343" t="inlineStr"/>
       <c r="N343" t="inlineStr">
@@ -21443,7 +22431,11 @@
         </is>
       </c>
       <c r="C344" t="inlineStr"/>
-      <c r="D344" t="inlineStr"/>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr"/>
       <c r="F344" t="inlineStr">
         <is>
@@ -21458,7 +22450,11 @@
       <c r="H344" t="inlineStr"/>
       <c r="I344" t="inlineStr"/>
       <c r="J344" t="inlineStr"/>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr"/>
       <c r="M344" t="inlineStr"/>
       <c r="N344" t="inlineStr">
@@ -21485,7 +22481,11 @@
         </is>
       </c>
       <c r="C345" t="inlineStr"/>
-      <c r="D345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr"/>
       <c r="F345" t="inlineStr">
         <is>
@@ -21500,7 +22500,11 @@
       <c r="H345" t="inlineStr"/>
       <c r="I345" t="inlineStr"/>
       <c r="J345" t="inlineStr"/>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr"/>
       <c r="M345" t="inlineStr"/>
       <c r="N345" t="inlineStr">
@@ -21527,7 +22531,11 @@
         </is>
       </c>
       <c r="C346" t="inlineStr"/>
-      <c r="D346" t="inlineStr"/>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E346" t="inlineStr"/>
       <c r="F346" t="inlineStr">
         <is>
@@ -21542,7 +22550,11 @@
       <c r="H346" t="inlineStr"/>
       <c r="I346" t="inlineStr"/>
       <c r="J346" t="inlineStr"/>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr"/>
       <c r="M346" t="inlineStr"/>
       <c r="N346" t="inlineStr">
@@ -21569,7 +22581,11 @@
         </is>
       </c>
       <c r="C347" t="inlineStr"/>
-      <c r="D347" t="inlineStr"/>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E347" t="inlineStr"/>
       <c r="F347" t="inlineStr">
         <is>
@@ -21584,7 +22600,11 @@
       <c r="H347" t="inlineStr"/>
       <c r="I347" t="inlineStr"/>
       <c r="J347" t="inlineStr"/>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr"/>
       <c r="M347" t="inlineStr"/>
       <c r="N347" t="inlineStr">
@@ -21611,7 +22631,11 @@
         </is>
       </c>
       <c r="C348" t="inlineStr"/>
-      <c r="D348" t="inlineStr"/>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E348" t="inlineStr"/>
       <c r="F348" t="inlineStr">
         <is>
@@ -21626,7 +22650,11 @@
       <c r="H348" t="inlineStr"/>
       <c r="I348" t="inlineStr"/>
       <c r="J348" t="inlineStr"/>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr"/>
       <c r="M348" t="inlineStr"/>
       <c r="N348" t="inlineStr">
@@ -21653,7 +22681,11 @@
         </is>
       </c>
       <c r="C349" t="inlineStr"/>
-      <c r="D349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E349" t="inlineStr"/>
       <c r="F349" t="inlineStr">
         <is>
@@ -21668,7 +22700,11 @@
       <c r="H349" t="inlineStr"/>
       <c r="I349" t="inlineStr"/>
       <c r="J349" t="inlineStr"/>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr"/>
       <c r="M349" t="inlineStr"/>
       <c r="N349" t="inlineStr">
@@ -21695,7 +22731,11 @@
         </is>
       </c>
       <c r="C350" t="inlineStr"/>
-      <c r="D350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E350" t="inlineStr"/>
       <c r="F350" t="inlineStr">
         <is>
@@ -21710,7 +22750,11 @@
       <c r="H350" t="inlineStr"/>
       <c r="I350" t="inlineStr"/>
       <c r="J350" t="inlineStr"/>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr"/>
       <c r="M350" t="inlineStr"/>
       <c r="N350" t="inlineStr">
@@ -21768,7 +22812,11 @@
       </c>
       <c r="I351" t="inlineStr"/>
       <c r="J351" t="inlineStr"/>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>TMP_AUX_EST_ANE</t>
@@ -21807,7 +22855,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr"/>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E352" t="inlineStr"/>
       <c r="F352" t="inlineStr">
         <is>
@@ -21822,7 +22874,11 @@
       <c r="H352" t="inlineStr"/>
       <c r="I352" t="inlineStr"/>
       <c r="J352" t="inlineStr"/>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr"/>
       <c r="M352" t="inlineStr"/>
       <c r="N352" t="inlineStr">
@@ -21876,7 +22932,11 @@
       </c>
       <c r="I353" t="inlineStr"/>
       <c r="J353" t="inlineStr"/>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>UPD_FALLECIDOS_RENIEC_20530</t>
@@ -21911,7 +22971,11 @@
         </is>
       </c>
       <c r="C354" t="inlineStr"/>
-      <c r="D354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr"/>
       <c r="F354" t="inlineStr">
         <is>
@@ -21926,7 +22990,11 @@
       <c r="H354" t="inlineStr"/>
       <c r="I354" t="inlineStr"/>
       <c r="J354" t="inlineStr"/>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr"/>
       <c r="M354" t="inlineStr"/>
       <c r="N354" t="inlineStr">
@@ -21957,7 +23025,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr"/>
       <c r="F355" t="inlineStr">
         <is>
@@ -21972,7 +23044,11 @@
       <c r="H355" t="inlineStr"/>
       <c r="I355" t="inlineStr"/>
       <c r="J355" t="inlineStr"/>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr"/>
       <c r="M355" t="inlineStr"/>
       <c r="N355" t="inlineStr"/>
@@ -21995,7 +23071,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr"/>
       <c r="F356" t="inlineStr">
         <is>
@@ -22010,7 +23090,11 @@
       <c r="H356" t="inlineStr"/>
       <c r="I356" t="inlineStr"/>
       <c r="J356" t="inlineStr"/>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr"/>
       <c r="M356" t="inlineStr"/>
       <c r="N356" t="inlineStr"/>
@@ -22023,7 +23107,11 @@
           <t>355</t>
         </is>
       </c>
-      <c r="B357" t="inlineStr"/>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C357" t="inlineStr"/>
       <c r="D357" t="inlineStr">
         <is>
@@ -22048,7 +23136,11 @@
       <c r="H357" t="inlineStr"/>
       <c r="I357" t="inlineStr"/>
       <c r="J357" t="inlineStr"/>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr"/>
       <c r="M357" t="inlineStr">
         <is>
@@ -22065,7 +23157,11 @@
           <t>356</t>
         </is>
       </c>
-      <c r="B358" t="inlineStr"/>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C358" t="inlineStr"/>
       <c r="D358" t="inlineStr">
         <is>
@@ -22090,7 +23186,11 @@
       <c r="H358" t="inlineStr"/>
       <c r="I358" t="inlineStr"/>
       <c r="J358" t="inlineStr"/>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr"/>
       <c r="M358" t="inlineStr">
         <is>
@@ -22107,7 +23207,11 @@
           <t>357</t>
         </is>
       </c>
-      <c r="B359" t="inlineStr"/>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C359" t="inlineStr"/>
       <c r="D359" t="inlineStr">
         <is>
@@ -22132,7 +23236,11 @@
       <c r="H359" t="inlineStr"/>
       <c r="I359" t="inlineStr"/>
       <c r="J359" t="inlineStr"/>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr"/>
       <c r="M359" t="inlineStr">
         <is>
@@ -22157,7 +23265,11 @@
           <t>358</t>
         </is>
       </c>
-      <c r="B360" t="inlineStr"/>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C360" t="inlineStr"/>
       <c r="D360" t="inlineStr">
         <is>
@@ -22182,7 +23294,11 @@
       <c r="H360" t="inlineStr"/>
       <c r="I360" t="inlineStr"/>
       <c r="J360" t="inlineStr"/>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr"/>
       <c r="M360" t="inlineStr">
         <is>
@@ -22199,7 +23315,11 @@
           <t>359</t>
         </is>
       </c>
-      <c r="B361" t="inlineStr"/>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C361" t="inlineStr"/>
       <c r="D361" t="inlineStr">
         <is>
@@ -22224,7 +23344,11 @@
       <c r="H361" t="inlineStr"/>
       <c r="I361" t="inlineStr"/>
       <c r="J361" t="inlineStr"/>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr"/>
       <c r="M361" t="inlineStr">
         <is>
@@ -22241,7 +23365,11 @@
           <t>360</t>
         </is>
       </c>
-      <c r="B362" t="inlineStr"/>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C362" t="inlineStr"/>
       <c r="D362" t="inlineStr">
         <is>
@@ -22266,7 +23394,11 @@
       <c r="H362" t="inlineStr"/>
       <c r="I362" t="inlineStr"/>
       <c r="J362" t="inlineStr"/>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr"/>
       <c r="M362" t="inlineStr">
         <is>
@@ -22283,7 +23415,11 @@
           <t>361</t>
         </is>
       </c>
-      <c r="B363" t="inlineStr"/>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C363" t="inlineStr"/>
       <c r="D363" t="inlineStr">
         <is>
@@ -22308,7 +23444,11 @@
       <c r="H363" t="inlineStr"/>
       <c r="I363" t="inlineStr"/>
       <c r="J363" t="inlineStr"/>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr"/>
       <c r="M363" t="inlineStr">
         <is>
@@ -22325,7 +23465,11 @@
           <t>362</t>
         </is>
       </c>
-      <c r="B364" t="inlineStr"/>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C364" t="inlineStr"/>
       <c r="D364" t="inlineStr">
         <is>
@@ -22350,7 +23494,11 @@
       <c r="H364" t="inlineStr"/>
       <c r="I364" t="inlineStr"/>
       <c r="J364" t="inlineStr"/>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr"/>
       <c r="M364" t="inlineStr">
         <is>
@@ -22367,7 +23515,11 @@
           <t>363</t>
         </is>
       </c>
-      <c r="B365" t="inlineStr"/>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C365" t="inlineStr"/>
       <c r="D365" t="inlineStr">
         <is>
@@ -22392,7 +23544,11 @@
       <c r="H365" t="inlineStr"/>
       <c r="I365" t="inlineStr"/>
       <c r="J365" t="inlineStr"/>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr"/>
       <c r="M365" t="inlineStr">
         <is>
@@ -22409,7 +23565,11 @@
           <t>364</t>
         </is>
       </c>
-      <c r="B366" t="inlineStr"/>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C366" t="inlineStr"/>
       <c r="D366" t="inlineStr">
         <is>
@@ -22434,7 +23594,11 @@
       <c r="H366" t="inlineStr"/>
       <c r="I366" t="inlineStr"/>
       <c r="J366" t="inlineStr"/>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr"/>
       <c r="M366" t="inlineStr">
         <is>
@@ -22451,7 +23615,11 @@
           <t>365</t>
         </is>
       </c>
-      <c r="B367" t="inlineStr"/>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C367" t="inlineStr"/>
       <c r="D367" t="inlineStr">
         <is>
@@ -22476,7 +23644,11 @@
       <c r="H367" t="inlineStr"/>
       <c r="I367" t="inlineStr"/>
       <c r="J367" t="inlineStr"/>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr"/>
       <c r="M367" t="inlineStr">
         <is>
@@ -22493,7 +23665,11 @@
           <t>366</t>
         </is>
       </c>
-      <c r="B368" t="inlineStr"/>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C368" t="inlineStr"/>
       <c r="D368" t="inlineStr">
         <is>
@@ -22518,7 +23694,11 @@
       <c r="H368" t="inlineStr"/>
       <c r="I368" t="inlineStr"/>
       <c r="J368" t="inlineStr"/>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr"/>
       <c r="M368" t="inlineStr">
         <is>
@@ -22535,7 +23715,11 @@
           <t>367</t>
         </is>
       </c>
-      <c r="B369" t="inlineStr"/>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C369" t="inlineStr"/>
       <c r="D369" t="inlineStr">
         <is>
@@ -22560,7 +23744,11 @@
       <c r="H369" t="inlineStr"/>
       <c r="I369" t="inlineStr"/>
       <c r="J369" t="inlineStr"/>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr"/>
       <c r="M369" t="inlineStr">
         <is>
@@ -22577,7 +23765,11 @@
           <t>368</t>
         </is>
       </c>
-      <c r="B370" t="inlineStr"/>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C370" t="inlineStr"/>
       <c r="D370" t="inlineStr">
         <is>
@@ -22602,7 +23794,11 @@
       <c r="H370" t="inlineStr"/>
       <c r="I370" t="inlineStr"/>
       <c r="J370" t="inlineStr"/>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr"/>
       <c r="M370" t="inlineStr">
         <is>
@@ -22619,7 +23815,11 @@
           <t>369</t>
         </is>
       </c>
-      <c r="B371" t="inlineStr"/>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C371" t="inlineStr"/>
       <c r="D371" t="inlineStr">
         <is>
@@ -22644,7 +23844,11 @@
       <c r="H371" t="inlineStr"/>
       <c r="I371" t="inlineStr"/>
       <c r="J371" t="inlineStr"/>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr"/>
       <c r="M371" t="inlineStr">
         <is>
@@ -22661,7 +23865,11 @@
           <t>370</t>
         </is>
       </c>
-      <c r="B372" t="inlineStr"/>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C372" t="inlineStr"/>
       <c r="D372" t="inlineStr">
         <is>
@@ -22686,7 +23894,11 @@
       <c r="H372" t="inlineStr"/>
       <c r="I372" t="inlineStr"/>
       <c r="J372" t="inlineStr"/>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr"/>
       <c r="M372" t="inlineStr">
         <is>
@@ -22703,7 +23915,11 @@
           <t>371</t>
         </is>
       </c>
-      <c r="B373" t="inlineStr"/>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C373" t="inlineStr"/>
       <c r="D373" t="inlineStr">
         <is>
@@ -22728,7 +23944,11 @@
       <c r="H373" t="inlineStr"/>
       <c r="I373" t="inlineStr"/>
       <c r="J373" t="inlineStr"/>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr"/>
       <c r="M373" t="inlineStr">
         <is>
@@ -22745,7 +23965,11 @@
           <t>372</t>
         </is>
       </c>
-      <c r="B374" t="inlineStr"/>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C374" t="inlineStr"/>
       <c r="D374" t="inlineStr">
         <is>
@@ -22770,7 +23994,11 @@
       <c r="H374" t="inlineStr"/>
       <c r="I374" t="inlineStr"/>
       <c r="J374" t="inlineStr"/>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr"/>
       <c r="M374" t="inlineStr">
         <is>
@@ -22787,7 +24015,11 @@
           <t>373</t>
         </is>
       </c>
-      <c r="B375" t="inlineStr"/>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C375" t="inlineStr"/>
       <c r="D375" t="inlineStr">
         <is>
@@ -22812,7 +24044,11 @@
       <c r="H375" t="inlineStr"/>
       <c r="I375" t="inlineStr"/>
       <c r="J375" t="inlineStr"/>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr"/>
       <c r="M375" t="inlineStr">
         <is>
@@ -22829,7 +24065,11 @@
           <t>374</t>
         </is>
       </c>
-      <c r="B376" t="inlineStr"/>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C376" t="inlineStr"/>
       <c r="D376" t="inlineStr">
         <is>
@@ -22854,7 +24094,11 @@
       <c r="H376" t="inlineStr"/>
       <c r="I376" t="inlineStr"/>
       <c r="J376" t="inlineStr"/>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr"/>
       <c r="M376" t="inlineStr">
         <is>
@@ -22877,7 +24121,11 @@
         </is>
       </c>
       <c r="C377" t="inlineStr"/>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr">
         <is>
@@ -22892,7 +24140,11 @@
       <c r="H377" t="inlineStr"/>
       <c r="I377" t="inlineStr"/>
       <c r="J377" t="inlineStr"/>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr"/>
       <c r="M377" t="inlineStr"/>
       <c r="N377" t="inlineStr">
@@ -22946,7 +24198,11 @@
       </c>
       <c r="I378" t="inlineStr"/>
       <c r="J378" t="inlineStr"/>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>TMP_PRE_AUX_DATO_CNCT</t>
@@ -23008,7 +24264,11 @@
       </c>
       <c r="I379" t="inlineStr"/>
       <c r="J379" t="inlineStr"/>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>TMP_PRE_REL_DATO_CNCT_PERS_1</t>
@@ -23070,7 +24330,11 @@
       </c>
       <c r="I380" t="inlineStr"/>
       <c r="J380" t="inlineStr"/>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>TMP_PRE_REL_DATO_CNCT_PERS_2</t>
@@ -23132,7 +24396,11 @@
       </c>
       <c r="I381" t="inlineStr"/>
       <c r="J381" t="inlineStr"/>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>Tmp_T727_Novedad_NETI</t>
@@ -23194,7 +24462,11 @@
       </c>
       <c r="I382" t="inlineStr"/>
       <c r="J382" t="inlineStr"/>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>Tmp_T727_Novedad_NETI</t>
@@ -23229,7 +24501,11 @@
         </is>
       </c>
       <c r="C383" t="inlineStr"/>
-      <c r="D383" t="inlineStr"/>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="inlineStr">
         <is>
@@ -23244,7 +24520,11 @@
       <c r="H383" t="inlineStr"/>
       <c r="I383" t="inlineStr"/>
       <c r="J383" t="inlineStr"/>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr"/>
       <c r="M383" t="inlineStr"/>
       <c r="N383" t="inlineStr">
@@ -23298,7 +24578,11 @@
       </c>
       <c r="I384" t="inlineStr"/>
       <c r="J384" t="inlineStr"/>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>Tmp_T727_Novedad_Neti_D</t>
@@ -23333,7 +24617,11 @@
         </is>
       </c>
       <c r="C385" t="inlineStr"/>
-      <c r="D385" t="inlineStr"/>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="inlineStr">
         <is>
@@ -23348,7 +24636,11 @@
       <c r="H385" t="inlineStr"/>
       <c r="I385" t="inlineStr"/>
       <c r="J385" t="inlineStr"/>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr"/>
       <c r="M385" t="inlineStr"/>
       <c r="N385" t="inlineStr">
@@ -23375,7 +24667,11 @@
         </is>
       </c>
       <c r="C386" t="inlineStr"/>
-      <c r="D386" t="inlineStr"/>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="inlineStr">
         <is>
@@ -23390,7 +24686,11 @@
       <c r="H386" t="inlineStr"/>
       <c r="I386" t="inlineStr"/>
       <c r="J386" t="inlineStr"/>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr"/>
       <c r="M386" t="inlineStr"/>
       <c r="N386" t="inlineStr">
@@ -23417,7 +24717,11 @@
         </is>
       </c>
       <c r="C387" t="inlineStr"/>
-      <c r="D387" t="inlineStr"/>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="inlineStr">
         <is>
@@ -23432,7 +24736,11 @@
       <c r="H387" t="inlineStr"/>
       <c r="I387" t="inlineStr"/>
       <c r="J387" t="inlineStr"/>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr"/>
       <c r="M387" t="inlineStr"/>
       <c r="N387" t="inlineStr">
@@ -23486,7 +24794,11 @@
       </c>
       <c r="I388" t="inlineStr"/>
       <c r="J388" t="inlineStr"/>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>TMP_T732_NOVEDAD_AUX_INS; TMP_T732_NOVEDAD_AUX_INS_DOCU</t>
@@ -23521,7 +24833,11 @@
         </is>
       </c>
       <c r="C389" t="inlineStr"/>
-      <c r="D389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="inlineStr">
         <is>
@@ -23536,7 +24852,11 @@
       <c r="H389" t="inlineStr"/>
       <c r="I389" t="inlineStr"/>
       <c r="J389" t="inlineStr"/>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr"/>
       <c r="M389" t="inlineStr"/>
       <c r="N389" t="inlineStr">
@@ -23563,7 +24883,11 @@
         </is>
       </c>
       <c r="C390" t="inlineStr"/>
-      <c r="D390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E390" t="inlineStr"/>
       <c r="F390" t="inlineStr">
         <is>
@@ -23578,7 +24902,11 @@
       <c r="H390" t="inlineStr"/>
       <c r="I390" t="inlineStr"/>
       <c r="J390" t="inlineStr"/>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr"/>
       <c r="M390" t="inlineStr"/>
       <c r="N390" t="inlineStr">
@@ -23632,7 +24960,11 @@
       </c>
       <c r="I391" t="inlineStr"/>
       <c r="J391" t="inlineStr"/>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>TMP_T733_NOVEDAD_AUX_INS; TMP_T733_NOVEDAD_AUX_INS_DOCU</t>
@@ -23667,7 +24999,11 @@
         </is>
       </c>
       <c r="C392" t="inlineStr"/>
-      <c r="D392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E392" t="inlineStr"/>
       <c r="F392" t="inlineStr">
         <is>
@@ -23682,7 +25018,11 @@
       <c r="H392" t="inlineStr"/>
       <c r="I392" t="inlineStr"/>
       <c r="J392" t="inlineStr"/>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr"/>
       <c r="M392" t="inlineStr"/>
       <c r="N392" t="inlineStr">
@@ -23736,7 +25076,11 @@
       </c>
       <c r="I393" t="inlineStr"/>
       <c r="J393" t="inlineStr"/>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>TMP_DET_NULI_AFIL_LOAD</t>
@@ -23771,7 +25115,11 @@
         </is>
       </c>
       <c r="C394" t="inlineStr"/>
-      <c r="D394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E394" t="inlineStr"/>
       <c r="F394" t="inlineStr">
         <is>
@@ -23786,7 +25134,11 @@
       <c r="H394" t="inlineStr"/>
       <c r="I394" t="inlineStr"/>
       <c r="J394" t="inlineStr"/>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr"/>
       <c r="M394" t="inlineStr"/>
       <c r="N394" t="inlineStr">
@@ -23813,7 +25165,11 @@
         </is>
       </c>
       <c r="C395" t="inlineStr"/>
-      <c r="D395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E395" t="inlineStr"/>
       <c r="F395" t="inlineStr">
         <is>
@@ -23828,7 +25184,11 @@
       <c r="H395" t="inlineStr"/>
       <c r="I395" t="inlineStr"/>
       <c r="J395" t="inlineStr"/>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr"/>
       <c r="M395" t="inlineStr"/>
       <c r="N395" t="inlineStr">
@@ -23886,7 +25246,11 @@
       </c>
       <c r="I396" t="inlineStr"/>
       <c r="J396" t="inlineStr"/>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>TMP_REL_EMPL_ACTI_ECON</t>
@@ -23948,7 +25312,11 @@
       </c>
       <c r="I397" t="inlineStr"/>
       <c r="J397" t="inlineStr"/>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>REL_VNCL_LABO_AFP; TMP_REL_VNCL_LABO_AFP_LOAD</t>
@@ -23977,7 +25345,11 @@
           <t>396</t>
         </is>
       </c>
-      <c r="B398" t="inlineStr"/>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C398" t="inlineStr"/>
       <c r="D398" t="inlineStr">
         <is>
@@ -24002,7 +25374,11 @@
       <c r="H398" t="inlineStr"/>
       <c r="I398" t="inlineStr"/>
       <c r="J398" t="inlineStr"/>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr"/>
       <c r="M398" t="inlineStr">
         <is>
@@ -24019,7 +25395,11 @@
           <t>397</t>
         </is>
       </c>
-      <c r="B399" t="inlineStr"/>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C399" t="inlineStr"/>
       <c r="D399" t="inlineStr">
         <is>
@@ -24044,7 +25424,11 @@
       <c r="H399" t="inlineStr"/>
       <c r="I399" t="inlineStr"/>
       <c r="J399" t="inlineStr"/>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr"/>
       <c r="M399" t="inlineStr">
         <is>
@@ -24061,7 +25445,11 @@
           <t>398</t>
         </is>
       </c>
-      <c r="B400" t="inlineStr"/>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C400" t="inlineStr"/>
       <c r="D400" t="inlineStr">
         <is>
@@ -24086,7 +25474,11 @@
       <c r="H400" t="inlineStr"/>
       <c r="I400" t="inlineStr"/>
       <c r="J400" t="inlineStr"/>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr"/>
       <c r="M400" t="inlineStr">
         <is>
@@ -24111,7 +25503,11 @@
           <t>399</t>
         </is>
       </c>
-      <c r="B401" t="inlineStr"/>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C401" t="inlineStr"/>
       <c r="D401" t="inlineStr">
         <is>
@@ -24136,7 +25532,11 @@
       <c r="H401" t="inlineStr"/>
       <c r="I401" t="inlineStr"/>
       <c r="J401" t="inlineStr"/>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr"/>
       <c r="M401" t="inlineStr">
         <is>
@@ -24153,7 +25553,11 @@
           <t>400</t>
         </is>
       </c>
-      <c r="B402" t="inlineStr"/>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C402" t="inlineStr"/>
       <c r="D402" t="inlineStr">
         <is>
@@ -24178,7 +25582,11 @@
       <c r="H402" t="inlineStr"/>
       <c r="I402" t="inlineStr"/>
       <c r="J402" t="inlineStr"/>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr"/>
       <c r="M402" t="inlineStr">
         <is>
@@ -24195,7 +25603,11 @@
           <t>401</t>
         </is>
       </c>
-      <c r="B403" t="inlineStr"/>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C403" t="inlineStr"/>
       <c r="D403" t="inlineStr">
         <is>
@@ -24220,7 +25632,11 @@
       <c r="H403" t="inlineStr"/>
       <c r="I403" t="inlineStr"/>
       <c r="J403" t="inlineStr"/>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr"/>
       <c r="M403" t="inlineStr">
         <is>
@@ -24237,7 +25653,11 @@
           <t>402</t>
         </is>
       </c>
-      <c r="B404" t="inlineStr"/>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C404" t="inlineStr"/>
       <c r="D404" t="inlineStr">
         <is>
@@ -24262,7 +25682,11 @@
       <c r="H404" t="inlineStr"/>
       <c r="I404" t="inlineStr"/>
       <c r="J404" t="inlineStr"/>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr"/>
       <c r="M404" t="inlineStr">
         <is>
@@ -24279,7 +25703,11 @@
           <t>403</t>
         </is>
       </c>
-      <c r="B405" t="inlineStr"/>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C405" t="inlineStr"/>
       <c r="D405" t="inlineStr">
         <is>
@@ -24304,7 +25732,11 @@
       <c r="H405" t="inlineStr"/>
       <c r="I405" t="inlineStr"/>
       <c r="J405" t="inlineStr"/>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr"/>
       <c r="M405" t="inlineStr">
         <is>
@@ -24321,7 +25753,11 @@
           <t>404</t>
         </is>
       </c>
-      <c r="B406" t="inlineStr"/>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C406" t="inlineStr"/>
       <c r="D406" t="inlineStr">
         <is>
@@ -24346,7 +25782,11 @@
       <c r="H406" t="inlineStr"/>
       <c r="I406" t="inlineStr"/>
       <c r="J406" t="inlineStr"/>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr"/>
       <c r="M406" t="inlineStr">
         <is>
@@ -24363,7 +25803,11 @@
           <t>405</t>
         </is>
       </c>
-      <c r="B407" t="inlineStr"/>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C407" t="inlineStr"/>
       <c r="D407" t="inlineStr">
         <is>
@@ -24388,7 +25832,11 @@
       <c r="H407" t="inlineStr"/>
       <c r="I407" t="inlineStr"/>
       <c r="J407" t="inlineStr"/>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr"/>
       <c r="M407" t="inlineStr">
         <is>
@@ -24405,7 +25853,11 @@
           <t>406</t>
         </is>
       </c>
-      <c r="B408" t="inlineStr"/>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
@@ -24430,7 +25882,11 @@
       <c r="H408" t="inlineStr"/>
       <c r="I408" t="inlineStr"/>
       <c r="J408" t="inlineStr"/>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr"/>
       <c r="M408" t="inlineStr">
         <is>
@@ -24447,7 +25903,11 @@
           <t>407</t>
         </is>
       </c>
-      <c r="B409" t="inlineStr"/>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
@@ -24472,7 +25932,11 @@
       <c r="H409" t="inlineStr"/>
       <c r="I409" t="inlineStr"/>
       <c r="J409" t="inlineStr"/>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr"/>
       <c r="M409" t="inlineStr">
         <is>
@@ -24489,7 +25953,11 @@
           <t>408</t>
         </is>
       </c>
-      <c r="B410" t="inlineStr"/>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
@@ -24514,7 +25982,11 @@
       <c r="H410" t="inlineStr"/>
       <c r="I410" t="inlineStr"/>
       <c r="J410" t="inlineStr"/>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr"/>
       <c r="M410" t="inlineStr">
         <is>
@@ -24531,7 +26003,11 @@
           <t>409</t>
         </is>
       </c>
-      <c r="B411" t="inlineStr"/>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
@@ -24556,7 +26032,11 @@
       <c r="H411" t="inlineStr"/>
       <c r="I411" t="inlineStr"/>
       <c r="J411" t="inlineStr"/>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr"/>
       <c r="M411" t="inlineStr">
         <is>
@@ -24573,7 +26053,11 @@
           <t>410</t>
         </is>
       </c>
-      <c r="B412" t="inlineStr"/>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C412" t="inlineStr"/>
       <c r="D412" t="inlineStr">
         <is>
@@ -24598,7 +26082,11 @@
       <c r="H412" t="inlineStr"/>
       <c r="I412" t="inlineStr"/>
       <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr"/>
       <c r="M412" t="inlineStr">
         <is>
@@ -24615,7 +26103,11 @@
           <t>411</t>
         </is>
       </c>
-      <c r="B413" t="inlineStr"/>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
@@ -24640,7 +26132,11 @@
       <c r="H413" t="inlineStr"/>
       <c r="I413" t="inlineStr"/>
       <c r="J413" t="inlineStr"/>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr"/>
       <c r="M413" t="inlineStr">
         <is>
@@ -24657,7 +26153,11 @@
           <t>412</t>
         </is>
       </c>
-      <c r="B414" t="inlineStr"/>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C414" t="inlineStr"/>
       <c r="D414" t="inlineStr">
         <is>
@@ -24682,7 +26182,11 @@
       <c r="H414" t="inlineStr"/>
       <c r="I414" t="inlineStr"/>
       <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr"/>
       <c r="M414" t="inlineStr">
         <is>
@@ -24699,7 +26203,11 @@
           <t>413</t>
         </is>
       </c>
-      <c r="B415" t="inlineStr"/>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr">
         <is>
@@ -24724,7 +26232,11 @@
       <c r="H415" t="inlineStr"/>
       <c r="I415" t="inlineStr"/>
       <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr"/>
       <c r="M415" t="inlineStr">
         <is>
@@ -24741,7 +26253,11 @@
           <t>414</t>
         </is>
       </c>
-      <c r="B416" t="inlineStr"/>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr">
         <is>
@@ -24766,7 +26282,11 @@
       <c r="H416" t="inlineStr"/>
       <c r="I416" t="inlineStr"/>
       <c r="J416" t="inlineStr"/>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr"/>
       <c r="M416" t="inlineStr">
         <is>
@@ -24783,7 +26303,11 @@
           <t>415</t>
         </is>
       </c>
-      <c r="B417" t="inlineStr"/>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr">
         <is>
@@ -24808,7 +26332,11 @@
       <c r="H417" t="inlineStr"/>
       <c r="I417" t="inlineStr"/>
       <c r="J417" t="inlineStr"/>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr"/>
       <c r="M417" t="inlineStr">
         <is>
@@ -24835,7 +26363,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr"/>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="inlineStr">
         <is>
@@ -24850,7 +26382,11 @@
       <c r="H418" t="inlineStr"/>
       <c r="I418" t="inlineStr"/>
       <c r="J418" t="inlineStr"/>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr"/>
       <c r="M418" t="inlineStr"/>
       <c r="N418" t="inlineStr">
@@ -24877,7 +26413,11 @@
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
-      <c r="D419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E419" t="inlineStr"/>
       <c r="F419" t="inlineStr">
         <is>
@@ -24892,7 +26432,11 @@
       <c r="H419" t="inlineStr"/>
       <c r="I419" t="inlineStr"/>
       <c r="J419" t="inlineStr"/>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr"/>
       <c r="M419" t="inlineStr"/>
       <c r="N419" t="inlineStr">
@@ -24919,7 +26463,11 @@
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
-      <c r="D420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E420" t="inlineStr"/>
       <c r="F420" t="inlineStr">
         <is>
@@ -24934,7 +26482,11 @@
       <c r="H420" t="inlineStr"/>
       <c r="I420" t="inlineStr"/>
       <c r="J420" t="inlineStr"/>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr"/>
       <c r="M420" t="inlineStr"/>
       <c r="N420" t="inlineStr">
@@ -24965,7 +26517,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D421" t="inlineStr"/>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E421" t="inlineStr"/>
       <c r="F421" t="inlineStr">
         <is>
@@ -24980,7 +26536,11 @@
       <c r="H421" t="inlineStr"/>
       <c r="I421" t="inlineStr"/>
       <c r="J421" t="inlineStr"/>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr"/>
       <c r="M421" t="inlineStr"/>
       <c r="N421" t="inlineStr">
@@ -25011,7 +26571,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D422" t="inlineStr"/>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E422" t="inlineStr"/>
       <c r="F422" t="inlineStr">
         <is>
@@ -25026,7 +26590,11 @@
       <c r="H422" t="inlineStr"/>
       <c r="I422" t="inlineStr"/>
       <c r="J422" t="inlineStr"/>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr"/>
       <c r="M422" t="inlineStr"/>
       <c r="N422" t="inlineStr">
@@ -25076,7 +26644,11 @@
       </c>
       <c r="I423" t="inlineStr"/>
       <c r="J423" t="inlineStr"/>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>tmpaportesdevueltos</t>
@@ -25138,7 +26710,11 @@
       </c>
       <c r="I424" t="inlineStr"/>
       <c r="J424" t="inlineStr"/>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>tmpaportesdevueltos</t>
@@ -25204,7 +26780,11 @@
       </c>
       <c r="I425" t="inlineStr"/>
       <c r="J425" t="inlineStr"/>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>RVL_TEMP_APOR_APORTANTE_T280</t>
@@ -25270,7 +26850,11 @@
       </c>
       <c r="I426" t="inlineStr"/>
       <c r="J426" t="inlineStr"/>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>RVL_TEMP_APORT_REL_LABO_T280</t>
@@ -25299,7 +26883,11 @@
           <t>425</t>
         </is>
       </c>
-      <c r="B427" t="inlineStr"/>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C427" t="inlineStr"/>
       <c r="D427" t="inlineStr">
         <is>
@@ -25328,7 +26916,11 @@
       </c>
       <c r="I427" t="inlineStr"/>
       <c r="J427" t="inlineStr"/>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>TEMP_MAE_PRES_PROV</t>
@@ -25390,7 +26982,11 @@
       </c>
       <c r="I428" t="inlineStr"/>
       <c r="J428" t="inlineStr"/>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>tmpaportecantdiastrab</t>
@@ -25419,7 +27015,11 @@
           <t>427</t>
         </is>
       </c>
-      <c r="B429" t="inlineStr"/>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C429" t="inlineStr"/>
       <c r="D429" t="inlineStr">
         <is>
@@ -25448,7 +27048,11 @@
       </c>
       <c r="I429" t="inlineStr"/>
       <c r="J429" t="inlineStr"/>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>TEMP_DET_DOCU_DGTL18; TEMP_DET_DOCU_DGTL18_TOT; TEMP_MAE_DOCU_DGTL18</t>
@@ -25477,7 +27081,11 @@
           <t>428</t>
         </is>
       </c>
-      <c r="B430" t="inlineStr"/>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr">
         <is>
@@ -25506,7 +27114,11 @@
       </c>
       <c r="I430" t="inlineStr"/>
       <c r="J430" t="inlineStr"/>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>TEMP_DET_DOCU_DGTL19; TEMP_DET_DOCU_DGTL19_TOT; TEMP_MAE_DOCU_DGTL19</t>
@@ -25535,7 +27147,11 @@
           <t>429</t>
         </is>
       </c>
-      <c r="B431" t="inlineStr"/>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C431" t="inlineStr"/>
       <c r="D431" t="inlineStr">
         <is>
@@ -25564,7 +27180,11 @@
       </c>
       <c r="I431" t="inlineStr"/>
       <c r="J431" t="inlineStr"/>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>TEMP_DET_DOCU_DGTL20; TEMP_DET_DOCU_DGTL20_TOT; TEMP_MAE_DOCU_DGTL20</t>
@@ -25593,7 +27213,11 @@
           <t>430</t>
         </is>
       </c>
-      <c r="B432" t="inlineStr"/>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Archivo plano (texto)</t>
+        </is>
+      </c>
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
@@ -25622,7 +27246,11 @@
       </c>
       <c r="I432" t="inlineStr"/>
       <c r="J432" t="inlineStr"/>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>TMP_EMPL_IRRE_0001</t>
@@ -25688,7 +27316,11 @@
       </c>
       <c r="I433" t="inlineStr"/>
       <c r="J433" t="inlineStr"/>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>MAE_PERS_TEMP_GNRAL_PAR_DETA; MAE_PERS_TEMP_SAEMPL_EMP</t>
@@ -25727,7 +27359,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E434" t="inlineStr"/>
       <c r="F434" t="inlineStr">
         <is>
@@ -25742,7 +27378,11 @@
       <c r="H434" t="inlineStr"/>
       <c r="I434" t="inlineStr"/>
       <c r="J434" t="inlineStr"/>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr"/>
       <c r="M434" t="inlineStr"/>
       <c r="N434" t="inlineStr"/>
@@ -25792,7 +27432,11 @@
       </c>
       <c r="I435" t="inlineStr"/>
       <c r="J435" t="inlineStr"/>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>TEMP_JOIN_18_SOL_LIQ</t>
@@ -25858,7 +27502,11 @@
       </c>
       <c r="I436" t="inlineStr"/>
       <c r="J436" t="inlineStr"/>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>TEMP_JOIN_19_SOL_LIQ</t>
@@ -25924,7 +27572,11 @@
       </c>
       <c r="I437" t="inlineStr"/>
       <c r="J437" t="inlineStr"/>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>TEMP_JOIN_20_SOL_LIQ</t>
@@ -25990,7 +27642,11 @@
       </c>
       <c r="I438" t="inlineStr"/>
       <c r="J438" t="inlineStr"/>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>TMP_DIF_LIQU_NSP</t>
@@ -26056,7 +27712,11 @@
       </c>
       <c r="I439" t="inlineStr"/>
       <c r="J439" t="inlineStr"/>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>TMP_DIF_LIQU_NSP2</t>
@@ -26122,7 +27782,11 @@
       </c>
       <c r="I440" t="inlineStr"/>
       <c r="J440" t="inlineStr"/>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>TMP_DIF_LIQU_NSP3</t>
@@ -26188,7 +27852,11 @@
       </c>
       <c r="I441" t="inlineStr"/>
       <c r="J441" t="inlineStr"/>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>mae_proc</t>
@@ -26254,7 +27922,11 @@
       </c>
       <c r="I442" t="inlineStr"/>
       <c r="J442" t="inlineStr"/>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>AUX_PROC_EVA_PERS</t>
@@ -26293,7 +27965,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D443" t="inlineStr"/>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E443" t="inlineStr"/>
       <c r="F443" t="inlineStr">
         <is>
@@ -26308,7 +27984,11 @@
       <c r="H443" t="inlineStr"/>
       <c r="I443" t="inlineStr"/>
       <c r="J443" t="inlineStr"/>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr"/>
       <c r="M443" t="inlineStr"/>
       <c r="N443" t="inlineStr">
@@ -26339,7 +28019,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D444" t="inlineStr"/>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E444" t="inlineStr"/>
       <c r="F444" t="inlineStr">
         <is>
@@ -26354,7 +28038,11 @@
       <c r="H444" t="inlineStr"/>
       <c r="I444" t="inlineStr"/>
       <c r="J444" t="inlineStr"/>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr"/>
       <c r="M444" t="inlineStr"/>
       <c r="N444" t="inlineStr">
@@ -26385,7 +28073,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D445" t="inlineStr"/>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E445" t="inlineStr"/>
       <c r="F445" t="inlineStr">
         <is>
@@ -26400,7 +28092,11 @@
       <c r="H445" t="inlineStr"/>
       <c r="I445" t="inlineStr"/>
       <c r="J445" t="inlineStr"/>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr"/>
       <c r="M445" t="inlineStr"/>
       <c r="N445" t="inlineStr">
@@ -26421,7 +28117,11 @@
           <t>444</t>
         </is>
       </c>
-      <c r="B446" t="inlineStr"/>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C446" t="inlineStr"/>
       <c r="D446" t="inlineStr">
         <is>
@@ -26450,7 +28150,11 @@
       </c>
       <c r="I446" t="inlineStr"/>
       <c r="J446" t="inlineStr"/>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>MAE_PERS_TEMP_BONO; MAE_PERS_TEMP_SOLI</t>
@@ -26516,7 +28220,11 @@
       </c>
       <c r="I447" t="inlineStr"/>
       <c r="J447" t="inlineStr"/>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>MAD_TEMPAPORTDECL_T280</t>
@@ -26582,7 +28290,11 @@
       </c>
       <c r="I448" t="inlineStr"/>
       <c r="J448" t="inlineStr"/>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>MAD_TEMP_APORPERIAPORT_T280; tmp_aportacionsys_param_t280</t>
@@ -26648,7 +28360,11 @@
       </c>
       <c r="I449" t="inlineStr"/>
       <c r="J449" t="inlineStr"/>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>REMUNERACION_MCCIA_T280</t>
@@ -26710,7 +28426,11 @@
       </c>
       <c r="I450" t="inlineStr"/>
       <c r="J450" t="inlineStr"/>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>TMP_CONTACTO_PERSONA_MAF; TMP_DIRECCION_PERSONA_MAF; TMP_DOCUMENTO_EMITIDO_MAF; TMP_PERSONA_MAF; TMP_RES_IPSS_MAF; TMP_TRAMITE_MAF</t>
@@ -26768,7 +28488,11 @@
       </c>
       <c r="I451" t="inlineStr"/>
       <c r="J451" t="inlineStr"/>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>TMP_CONTACTO_PERSONA_MAF; TMP_DIRECCION_PERSONA_MAF; TMP_DOCUMENTO_EMITIDO_MAF; TMP_PERSONA_MAF; TMP_RES_IPSS_MAF; TMP_TRAMITE_MAF</t>
@@ -26803,7 +28527,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E452" t="inlineStr"/>
       <c r="F452" t="inlineStr">
         <is>
@@ -26818,7 +28546,11 @@
       <c r="H452" t="inlineStr"/>
       <c r="I452" t="inlineStr"/>
       <c r="J452" t="inlineStr"/>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr"/>
       <c r="M452" t="inlineStr"/>
       <c r="N452" t="inlineStr">
@@ -26839,7 +28571,11 @@
           <t>451</t>
         </is>
       </c>
-      <c r="B453" t="inlineStr"/>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C453" t="inlineStr"/>
       <c r="D453" t="inlineStr">
         <is>
@@ -26868,7 +28604,11 @@
       </c>
       <c r="I453" t="inlineStr"/>
       <c r="J453" t="inlineStr"/>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>TEMP_TD_DETA_LIQUI_18; TEMP_TP_EXP; TEMP_TP_FAM_SOL; TEMP_TP_PARAMETRO_18; TEMP_TP_PEN_DEP; TEMP_TP_RES_LIQ; TEMP_TP_SOL; TEMP_TR_PARAM_PERSONAL_LIQ18; TEMP_TR_PARA_RESU_LIQUI_18</t>
@@ -26897,7 +28637,11 @@
           <t>452</t>
         </is>
       </c>
-      <c r="B454" t="inlineStr"/>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C454" t="inlineStr"/>
       <c r="D454" t="inlineStr">
         <is>
@@ -26926,7 +28670,11 @@
       </c>
       <c r="I454" t="inlineStr"/>
       <c r="J454" t="inlineStr"/>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>TEMP_TD_DETA_LIQUI_19; TEMP_TP_EXP; TEMP_TP_FAM_SOL; TEMP_TP_PARAMETRO_19; TEMP_TP_PEN_DEP; TEMP_TP_RES_LIQ; TEMP_TP_SOL; TEMP_TR_PARAM_PERSONAL_LIQ19; TEMP_TR_PARA_RESU_LIQUI_19</t>
@@ -26955,7 +28703,11 @@
           <t>453</t>
         </is>
       </c>
-      <c r="B455" t="inlineStr"/>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C455" t="inlineStr"/>
       <c r="D455" t="inlineStr">
         <is>
@@ -26984,7 +28736,11 @@
       </c>
       <c r="I455" t="inlineStr"/>
       <c r="J455" t="inlineStr"/>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>TEMP_TD_DETA_LIQUI_20; TEMP_TP_EXP; TEMP_TP_FAM_SOL; TEMP_TP_PARAMETRO_20; TEMP_TP_PEN_DEP; TEMP_TP_RES_LIQ; TEMP_TP_SOL; TEMP_TR_PARAM_PERSONAL_LIQ20; TEMP_TR_PARA_RESU_LIQUI_20</t>
@@ -27050,7 +28806,11 @@
       </c>
       <c r="I456" t="inlineStr"/>
       <c r="J456" t="inlineStr"/>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>NSTD_TEMP_EXPDNTES; PERSONASYS_TMP_PERSONA</t>
@@ -27079,7 +28839,11 @@
           <t>455</t>
         </is>
       </c>
-      <c r="B457" t="inlineStr"/>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C457" t="inlineStr"/>
       <c r="D457" t="inlineStr">
         <is>
@@ -27108,7 +28872,11 @@
       </c>
       <c r="I457" t="inlineStr"/>
       <c r="J457" t="inlineStr"/>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>TEMP_TC_SECTOR_OCUPACIONAL; TEMP_TR_INFORME_VERIFICACION; TEMP_TR_MOTIVO_CESE</t>
@@ -27137,7 +28905,11 @@
           <t>456</t>
         </is>
       </c>
-      <c r="B458" t="inlineStr"/>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C458" t="inlineStr"/>
       <c r="D458" t="inlineStr">
         <is>
@@ -27166,7 +28938,11 @@
       </c>
       <c r="I458" t="inlineStr"/>
       <c r="J458" t="inlineStr"/>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>TEMP_TR_APORTE_REMUNERACION</t>
@@ -27195,7 +28971,11 @@
           <t>457</t>
         </is>
       </c>
-      <c r="B459" t="inlineStr"/>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C459" t="inlineStr"/>
       <c r="D459" t="inlineStr">
         <is>
@@ -27224,7 +29004,11 @@
       </c>
       <c r="I459" t="inlineStr"/>
       <c r="J459" t="inlineStr"/>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>TEMP_TP_DATOS_DESAFILIACION</t>
@@ -27282,7 +29066,11 @@
       </c>
       <c r="I460" t="inlineStr"/>
       <c r="J460" t="inlineStr"/>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>NSTD_TEMP_MONEDA; TEMP_DETALLE_SOLICITUD; TEMP_EMPLEADOR_HISTORICO; TEMP_MES_SOLICITUD</t>
@@ -27344,7 +29132,11 @@
       </c>
       <c r="I461" t="inlineStr"/>
       <c r="J461" t="inlineStr"/>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>EXT_POLIZA_SCTR_001_2</t>
@@ -27406,7 +29198,11 @@
       </c>
       <c r="I462" t="inlineStr"/>
       <c r="J462" t="inlineStr"/>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>MAE_POLI_TMP_EMPLEADOR_2</t>
@@ -27435,7 +29231,11 @@
           <t>461</t>
         </is>
       </c>
-      <c r="B463" t="inlineStr"/>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C463" t="inlineStr"/>
       <c r="D463" t="inlineStr">
         <is>
@@ -27464,7 +29264,11 @@
       </c>
       <c r="I463" t="inlineStr"/>
       <c r="J463" t="inlineStr"/>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>MAE_PERS_TEMP_BONO; MAE_TEMP_TIPO_BONO</t>
@@ -27530,7 +29334,11 @@
       </c>
       <c r="I464" t="inlineStr"/>
       <c r="J464" t="inlineStr"/>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>REL_PERS_DOCU_TEMP_COM</t>
@@ -27559,7 +29367,11 @@
           <t>463</t>
         </is>
       </c>
-      <c r="B465" t="inlineStr"/>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>(origen parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="C465" t="inlineStr"/>
       <c r="D465" t="inlineStr">
         <is>
@@ -27588,7 +29400,11 @@
       </c>
       <c r="I465" t="inlineStr"/>
       <c r="J465" t="inlineStr"/>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>NSTD_TEMP_TUFO</t>
@@ -27646,7 +29462,11 @@
       </c>
       <c r="I466" t="inlineStr"/>
       <c r="J466" t="inlineStr"/>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>tmpaportecantdiastrab</t>
@@ -27712,7 +29532,11 @@
       </c>
       <c r="I467" t="inlineStr"/>
       <c r="J467" t="inlineStr"/>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>TMP_DIF_SOLI_NSP_18</t>
@@ -27778,7 +29602,11 @@
       </c>
       <c r="I468" t="inlineStr"/>
       <c r="J468" t="inlineStr"/>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>TMP_DIF_NSP_SOLI2_18</t>
@@ -27844,7 +29672,11 @@
       </c>
       <c r="I469" t="inlineStr"/>
       <c r="J469" t="inlineStr"/>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>TMP_SOLICITANTE_NSP_18</t>
@@ -27910,7 +29742,11 @@
       </c>
       <c r="I470" t="inlineStr"/>
       <c r="J470" t="inlineStr"/>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>TMP_DIF_NSP_SOLI3_18</t>
@@ -27976,7 +29812,11 @@
       </c>
       <c r="I471" t="inlineStr"/>
       <c r="J471" t="inlineStr"/>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>TMP_DIF_SOLI_NSP_19</t>
@@ -28042,7 +29882,11 @@
       </c>
       <c r="I472" t="inlineStr"/>
       <c r="J472" t="inlineStr"/>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>TMP_DIF_NSP_SOLI2_19</t>
@@ -28108,7 +29952,11 @@
       </c>
       <c r="I473" t="inlineStr"/>
       <c r="J473" t="inlineStr"/>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>TMP_SOLICITANTE_NSP_19</t>
@@ -28174,7 +30022,11 @@
       </c>
       <c r="I474" t="inlineStr"/>
       <c r="J474" t="inlineStr"/>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>TMP_DIF_NSP_SOLI3_19</t>
@@ -28240,7 +30092,11 @@
       </c>
       <c r="I475" t="inlineStr"/>
       <c r="J475" t="inlineStr"/>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>TMP_DIF_NSP_SOLI4_19</t>
@@ -28306,7 +30162,11 @@
       </c>
       <c r="I476" t="inlineStr"/>
       <c r="J476" t="inlineStr"/>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>TMP_AUX_PERI_NSP_2_19</t>
@@ -28372,7 +30232,11 @@
       </c>
       <c r="I477" t="inlineStr"/>
       <c r="J477" t="inlineStr"/>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>TMP_AUX_PERI_NSP_3_19</t>
@@ -28438,7 +30302,11 @@
       </c>
       <c r="I478" t="inlineStr"/>
       <c r="J478" t="inlineStr"/>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>TMP_AUX_PERI_NSP_APRT_19</t>
@@ -28504,7 +30372,11 @@
       </c>
       <c r="I479" t="inlineStr"/>
       <c r="J479" t="inlineStr"/>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>TMP_AUX_PERI_NSP_APRT_19_REMU</t>
@@ -28570,7 +30442,11 @@
       </c>
       <c r="I480" t="inlineStr"/>
       <c r="J480" t="inlineStr"/>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>TMP_OBJETO_NSP_APRT_19</t>
@@ -28636,7 +30512,11 @@
       </c>
       <c r="I481" t="inlineStr"/>
       <c r="J481" t="inlineStr"/>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>TMP_AUX_PERI_NSP_APRT_19_RESM</t>
@@ -28702,7 +30582,11 @@
       </c>
       <c r="I482" t="inlineStr"/>
       <c r="J482" t="inlineStr"/>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>TMP_DIF_SOLI_NSP_20</t>
@@ -28768,7 +30652,11 @@
       </c>
       <c r="I483" t="inlineStr"/>
       <c r="J483" t="inlineStr"/>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>TMP_DIF_NSP_SOLI2_20</t>
@@ -28834,7 +30722,11 @@
       </c>
       <c r="I484" t="inlineStr"/>
       <c r="J484" t="inlineStr"/>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>TMP_SOLICITANTE_NSP_20</t>
@@ -28900,7 +30792,11 @@
       </c>
       <c r="I485" t="inlineStr"/>
       <c r="J485" t="inlineStr"/>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>TMP_DIF_NSP_SOLI3_20</t>
@@ -28939,7 +30835,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D486" t="inlineStr"/>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E486" t="inlineStr"/>
       <c r="F486" t="inlineStr">
         <is>
@@ -28954,7 +30854,11 @@
       <c r="H486" t="inlineStr"/>
       <c r="I486" t="inlineStr"/>
       <c r="J486" t="inlineStr"/>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr"/>
       <c r="M486" t="inlineStr"/>
       <c r="N486" t="inlineStr">
@@ -29012,7 +30916,11 @@
       </c>
       <c r="I487" t="inlineStr"/>
       <c r="J487" t="inlineStr"/>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>TMP_DIF_SOLI_NSP_20</t>
@@ -29051,7 +30959,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D488" t="inlineStr"/>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E488" t="inlineStr"/>
       <c r="F488" t="inlineStr">
         <is>
@@ -29066,7 +30978,11 @@
       <c r="H488" t="inlineStr"/>
       <c r="I488" t="inlineStr"/>
       <c r="J488" t="inlineStr"/>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr"/>
       <c r="M488" t="inlineStr"/>
       <c r="N488" t="inlineStr">
@@ -29097,7 +31013,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D489" t="inlineStr"/>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E489" t="inlineStr"/>
       <c r="F489" t="inlineStr">
         <is>
@@ -29112,7 +31032,11 @@
       <c r="H489" t="inlineStr"/>
       <c r="I489" t="inlineStr"/>
       <c r="J489" t="inlineStr"/>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr"/>
       <c r="M489" t="inlineStr"/>
       <c r="N489" t="inlineStr">
@@ -29143,7 +31067,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D490" t="inlineStr"/>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E490" t="inlineStr"/>
       <c r="F490" t="inlineStr">
         <is>
@@ -29158,7 +31086,11 @@
       <c r="H490" t="inlineStr"/>
       <c r="I490" t="inlineStr"/>
       <c r="J490" t="inlineStr"/>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr"/>
       <c r="M490" t="inlineStr"/>
       <c r="N490" t="inlineStr">
@@ -29189,7 +31121,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D491" t="inlineStr"/>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E491" t="inlineStr"/>
       <c r="F491" t="inlineStr">
         <is>
@@ -29204,7 +31140,11 @@
       <c r="H491" t="inlineStr"/>
       <c r="I491" t="inlineStr"/>
       <c r="J491" t="inlineStr"/>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr"/>
       <c r="M491" t="inlineStr"/>
       <c r="N491" t="inlineStr">
@@ -29235,7 +31175,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D492" t="inlineStr"/>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E492" t="inlineStr"/>
       <c r="F492" t="inlineStr">
         <is>
@@ -29250,7 +31194,11 @@
       <c r="H492" t="inlineStr"/>
       <c r="I492" t="inlineStr"/>
       <c r="J492" t="inlineStr"/>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr"/>
       <c r="M492" t="inlineStr"/>
       <c r="N492" t="inlineStr">
@@ -29281,7 +31229,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D493" t="inlineStr"/>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E493" t="inlineStr"/>
       <c r="F493" t="inlineStr">
         <is>
@@ -29296,7 +31248,11 @@
       <c r="H493" t="inlineStr"/>
       <c r="I493" t="inlineStr"/>
       <c r="J493" t="inlineStr"/>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr"/>
       <c r="M493" t="inlineStr"/>
       <c r="N493" t="inlineStr">
@@ -29327,7 +31283,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D494" t="inlineStr"/>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E494" t="inlineStr"/>
       <c r="F494" t="inlineStr">
         <is>
@@ -29342,7 +31302,11 @@
       <c r="H494" t="inlineStr"/>
       <c r="I494" t="inlineStr"/>
       <c r="J494" t="inlineStr"/>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr"/>
       <c r="M494" t="inlineStr"/>
       <c r="N494" t="inlineStr">
@@ -29373,7 +31337,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D495" t="inlineStr"/>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E495" t="inlineStr"/>
       <c r="F495" t="inlineStr">
         <is>
@@ -29388,7 +31356,11 @@
       <c r="H495" t="inlineStr"/>
       <c r="I495" t="inlineStr"/>
       <c r="J495" t="inlineStr"/>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr"/>
       <c r="M495" t="inlineStr"/>
       <c r="N495" t="inlineStr">
@@ -29419,7 +31391,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D496" t="inlineStr"/>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E496" t="inlineStr"/>
       <c r="F496" t="inlineStr">
         <is>
@@ -29434,7 +31410,11 @@
       <c r="H496" t="inlineStr"/>
       <c r="I496" t="inlineStr"/>
       <c r="J496" t="inlineStr"/>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr"/>
       <c r="M496" t="inlineStr"/>
       <c r="N496" t="inlineStr">
@@ -29465,7 +31445,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D497" t="inlineStr"/>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E497" t="inlineStr"/>
       <c r="F497" t="inlineStr">
         <is>
@@ -29480,7 +31464,11 @@
       <c r="H497" t="inlineStr"/>
       <c r="I497" t="inlineStr"/>
       <c r="J497" t="inlineStr"/>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr"/>
       <c r="M497" t="inlineStr"/>
       <c r="N497" t="inlineStr">
@@ -29511,7 +31499,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D498" t="inlineStr"/>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E498" t="inlineStr"/>
       <c r="F498" t="inlineStr">
         <is>
@@ -29526,7 +31518,11 @@
       <c r="H498" t="inlineStr"/>
       <c r="I498" t="inlineStr"/>
       <c r="J498" t="inlineStr"/>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr"/>
       <c r="M498" t="inlineStr"/>
       <c r="N498" t="inlineStr">
@@ -29557,7 +31553,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D499" t="inlineStr"/>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E499" t="inlineStr"/>
       <c r="F499" t="inlineStr">
         <is>
@@ -29572,7 +31572,11 @@
       <c r="H499" t="inlineStr"/>
       <c r="I499" t="inlineStr"/>
       <c r="J499" t="inlineStr"/>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr"/>
       <c r="M499" t="inlineStr"/>
       <c r="N499" t="inlineStr">
@@ -29603,7 +31607,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D500" t="inlineStr"/>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E500" t="inlineStr"/>
       <c r="F500" t="inlineStr">
         <is>
@@ -29618,7 +31626,11 @@
       <c r="H500" t="inlineStr"/>
       <c r="I500" t="inlineStr"/>
       <c r="J500" t="inlineStr"/>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr"/>
       <c r="M500" t="inlineStr"/>
       <c r="N500" t="inlineStr">
@@ -29649,7 +31661,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D501" t="inlineStr"/>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E501" t="inlineStr"/>
       <c r="F501" t="inlineStr">
         <is>
@@ -29664,7 +31680,11 @@
       <c r="H501" t="inlineStr"/>
       <c r="I501" t="inlineStr"/>
       <c r="J501" t="inlineStr"/>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr"/>
       <c r="M501" t="inlineStr"/>
       <c r="N501" t="inlineStr">
@@ -29722,7 +31742,11 @@
       </c>
       <c r="I502" t="inlineStr"/>
       <c r="J502" t="inlineStr"/>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>TMP_BONO_DIFF</t>
@@ -29788,7 +31812,11 @@
       </c>
       <c r="I503" t="inlineStr"/>
       <c r="J503" t="inlineStr"/>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>TMP_DIFERENCIA_EXPE_NSBR</t>
@@ -29854,7 +31882,11 @@
       </c>
       <c r="I504" t="inlineStr"/>
       <c r="J504" t="inlineStr"/>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>TMP_DIFERENCIA_SOLI_NSBR</t>
@@ -29920,7 +31952,11 @@
       </c>
       <c r="I505" t="inlineStr"/>
       <c r="J505" t="inlineStr"/>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>TMP_DIFERENCIA_SOLI_NSBR_2</t>
@@ -29955,7 +31991,11 @@
         </is>
       </c>
       <c r="C506" t="inlineStr"/>
-      <c r="D506" t="inlineStr"/>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E506" t="inlineStr"/>
       <c r="F506" t="inlineStr">
         <is>
@@ -29970,7 +32010,11 @@
       <c r="H506" t="inlineStr"/>
       <c r="I506" t="inlineStr"/>
       <c r="J506" t="inlineStr"/>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr"/>
       <c r="M506" t="inlineStr"/>
       <c r="N506" t="inlineStr">
@@ -29997,7 +32041,11 @@
         </is>
       </c>
       <c r="C507" t="inlineStr"/>
-      <c r="D507" t="inlineStr"/>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E507" t="inlineStr"/>
       <c r="F507" t="inlineStr">
         <is>
@@ -30012,7 +32060,11 @@
       <c r="H507" t="inlineStr"/>
       <c r="I507" t="inlineStr"/>
       <c r="J507" t="inlineStr"/>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr"/>
       <c r="M507" t="inlineStr"/>
       <c r="N507" t="inlineStr">
@@ -30039,7 +32091,11 @@
         </is>
       </c>
       <c r="C508" t="inlineStr"/>
-      <c r="D508" t="inlineStr"/>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E508" t="inlineStr"/>
       <c r="F508" t="inlineStr">
         <is>
@@ -30054,7 +32110,11 @@
       <c r="H508" t="inlineStr"/>
       <c r="I508" t="inlineStr"/>
       <c r="J508" t="inlineStr"/>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr"/>
       <c r="M508" t="inlineStr"/>
       <c r="N508" t="inlineStr">
@@ -30077,7 +32137,11 @@
         </is>
       </c>
       <c r="C509" t="inlineStr"/>
-      <c r="D509" t="inlineStr"/>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E509" t="inlineStr"/>
       <c r="F509" t="inlineStr">
         <is>
@@ -30092,7 +32156,11 @@
       <c r="H509" t="inlineStr"/>
       <c r="I509" t="inlineStr"/>
       <c r="J509" t="inlineStr"/>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr"/>
       <c r="M509" t="inlineStr"/>
       <c r="N509" t="inlineStr">
@@ -30119,7 +32187,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D510" t="inlineStr"/>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E510" t="inlineStr"/>
       <c r="F510" t="inlineStr">
         <is>
@@ -30134,7 +32206,11 @@
       <c r="H510" t="inlineStr"/>
       <c r="I510" t="inlineStr"/>
       <c r="J510" t="inlineStr"/>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr"/>
       <c r="M510" t="inlineStr"/>
       <c r="N510" t="inlineStr">
@@ -30165,7 +32241,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D511" t="inlineStr"/>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E511" t="inlineStr"/>
       <c r="F511" t="inlineStr">
         <is>
@@ -30180,7 +32260,11 @@
       <c r="H511" t="inlineStr"/>
       <c r="I511" t="inlineStr"/>
       <c r="J511" t="inlineStr"/>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr"/>
       <c r="M511" t="inlineStr"/>
       <c r="N511" t="inlineStr">
@@ -30211,7 +32295,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D512" t="inlineStr"/>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E512" t="inlineStr"/>
       <c r="F512" t="inlineStr">
         <is>
@@ -30226,7 +32314,11 @@
       <c r="H512" t="inlineStr"/>
       <c r="I512" t="inlineStr"/>
       <c r="J512" t="inlineStr"/>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr"/>
       <c r="M512" t="inlineStr"/>
       <c r="N512" t="inlineStr">
@@ -30257,7 +32349,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D513" t="inlineStr"/>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E513" t="inlineStr"/>
       <c r="F513" t="inlineStr">
         <is>
@@ -30272,7 +32368,11 @@
       <c r="H513" t="inlineStr"/>
       <c r="I513" t="inlineStr"/>
       <c r="J513" t="inlineStr"/>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr"/>
       <c r="M513" t="inlineStr"/>
       <c r="N513" t="inlineStr">
@@ -30330,7 +32430,11 @@
       </c>
       <c r="I514" t="inlineStr"/>
       <c r="J514" t="inlineStr"/>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>AUX_VERI_DOCU_DIGI</t>
@@ -30396,7 +32500,11 @@
       </c>
       <c r="I515" t="inlineStr"/>
       <c r="J515" t="inlineStr"/>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>AUX_VERI_DOCU_DIGI</t>
@@ -30462,7 +32570,11 @@
       </c>
       <c r="I516" t="inlineStr"/>
       <c r="J516" t="inlineStr"/>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>AUX_VERI_DOCU_DIGI</t>
@@ -30501,7 +32613,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D517" t="inlineStr"/>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E517" t="inlineStr"/>
       <c r="F517" t="inlineStr">
         <is>
@@ -30516,7 +32632,11 @@
       <c r="H517" t="inlineStr"/>
       <c r="I517" t="inlineStr"/>
       <c r="J517" t="inlineStr"/>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr"/>
       <c r="M517" t="inlineStr"/>
       <c r="N517" t="inlineStr">
@@ -30547,7 +32667,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D518" t="inlineStr"/>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E518" t="inlineStr"/>
       <c r="F518" t="inlineStr">
         <is>
@@ -30562,7 +32686,11 @@
       <c r="H518" t="inlineStr"/>
       <c r="I518" t="inlineStr"/>
       <c r="J518" t="inlineStr"/>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr"/>
       <c r="M518" t="inlineStr"/>
       <c r="N518" t="inlineStr">
@@ -30593,7 +32721,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D519" t="inlineStr"/>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E519" t="inlineStr"/>
       <c r="F519" t="inlineStr">
         <is>
@@ -30608,7 +32740,11 @@
       <c r="H519" t="inlineStr"/>
       <c r="I519" t="inlineStr"/>
       <c r="J519" t="inlineStr"/>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr"/>
       <c r="M519" t="inlineStr"/>
       <c r="N519" t="inlineStr">
@@ -30662,7 +32798,11 @@
       </c>
       <c r="I520" t="inlineStr"/>
       <c r="J520" t="inlineStr"/>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>CTL_CARG_ARCHIV_EXT</t>
@@ -30697,7 +32837,11 @@
         </is>
       </c>
       <c r="C521" t="inlineStr"/>
-      <c r="D521" t="inlineStr"/>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E521" t="inlineStr"/>
       <c r="F521" t="inlineStr">
         <is>
@@ -30712,7 +32856,11 @@
       <c r="H521" t="inlineStr"/>
       <c r="I521" t="inlineStr"/>
       <c r="J521" t="inlineStr"/>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr"/>
       <c r="M521" t="inlineStr"/>
       <c r="N521" t="inlineStr">
@@ -30735,7 +32883,11 @@
         </is>
       </c>
       <c r="C522" t="inlineStr"/>
-      <c r="D522" t="inlineStr"/>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E522" t="inlineStr"/>
       <c r="F522" t="inlineStr">
         <is>
@@ -30750,7 +32902,11 @@
       <c r="H522" t="inlineStr"/>
       <c r="I522" t="inlineStr"/>
       <c r="J522" t="inlineStr"/>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr"/>
       <c r="M522" t="inlineStr"/>
       <c r="N522" t="inlineStr">
@@ -30792,7 +32948,11 @@
       <c r="H523" t="inlineStr"/>
       <c r="I523" t="inlineStr"/>
       <c r="J523" t="inlineStr"/>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr"/>
       <c r="M523" t="inlineStr"/>
       <c r="N523" t="inlineStr">
@@ -30815,7 +32975,11 @@
         </is>
       </c>
       <c r="C524" t="inlineStr"/>
-      <c r="D524" t="inlineStr"/>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E524" t="inlineStr"/>
       <c r="F524" t="inlineStr">
         <is>
@@ -30830,7 +32994,11 @@
       <c r="H524" t="inlineStr"/>
       <c r="I524" t="inlineStr"/>
       <c r="J524" t="inlineStr"/>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr"/>
       <c r="M524" t="inlineStr"/>
       <c r="N524" t="inlineStr">
@@ -30884,7 +33052,11 @@
       </c>
       <c r="I525" t="inlineStr"/>
       <c r="J525" t="inlineStr"/>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>AUX_SOLI_LDI</t>
@@ -30938,7 +33110,11 @@
       </c>
       <c r="I526" t="inlineStr"/>
       <c r="J526" t="inlineStr"/>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>CTL_CARG_ARCHIV_EXT</t>
@@ -31000,7 +33176,11 @@
       </c>
       <c r="I527" t="inlineStr"/>
       <c r="J527" t="inlineStr"/>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>MAE_POLI_SEGU</t>
@@ -31062,7 +33242,11 @@
       </c>
       <c r="I528" t="inlineStr"/>
       <c r="J528" t="inlineStr"/>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>REL_POLI_PERS</t>
@@ -31101,7 +33285,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D529" t="inlineStr"/>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E529" t="inlineStr"/>
       <c r="F529" t="inlineStr">
         <is>
@@ -31116,7 +33304,11 @@
       <c r="H529" t="inlineStr"/>
       <c r="I529" t="inlineStr"/>
       <c r="J529" t="inlineStr"/>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr"/>
       <c r="M529" t="inlineStr"/>
       <c r="N529" t="inlineStr">
@@ -31143,7 +33335,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D530" t="inlineStr"/>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E530" t="inlineStr"/>
       <c r="F530" t="inlineStr">
         <is>
@@ -31158,7 +33354,11 @@
       <c r="H530" t="inlineStr"/>
       <c r="I530" t="inlineStr"/>
       <c r="J530" t="inlineStr"/>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr"/>
       <c r="M530" t="inlineStr"/>
       <c r="N530" t="inlineStr">
@@ -31185,7 +33385,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D531" t="inlineStr"/>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E531" t="inlineStr"/>
       <c r="F531" t="inlineStr">
         <is>
@@ -31200,7 +33404,11 @@
       <c r="H531" t="inlineStr"/>
       <c r="I531" t="inlineStr"/>
       <c r="J531" t="inlineStr"/>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr"/>
       <c r="M531" t="inlineStr"/>
       <c r="N531" t="inlineStr">
@@ -31227,7 +33435,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D532" t="inlineStr"/>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E532" t="inlineStr"/>
       <c r="F532" t="inlineStr">
         <is>
@@ -31242,7 +33454,11 @@
       <c r="H532" t="inlineStr"/>
       <c r="I532" t="inlineStr"/>
       <c r="J532" t="inlineStr"/>
-      <c r="K532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L532" t="inlineStr"/>
       <c r="M532" t="inlineStr"/>
       <c r="N532" t="inlineStr">
@@ -31273,7 +33489,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D533" t="inlineStr"/>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E533" t="inlineStr"/>
       <c r="F533" t="inlineStr">
         <is>
@@ -31288,7 +33508,11 @@
       <c r="H533" t="inlineStr"/>
       <c r="I533" t="inlineStr"/>
       <c r="J533" t="inlineStr"/>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr"/>
       <c r="M533" t="inlineStr"/>
       <c r="N533" t="inlineStr">
@@ -31319,7 +33543,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D534" t="inlineStr"/>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E534" t="inlineStr"/>
       <c r="F534" t="inlineStr">
         <is>
@@ -31334,7 +33562,11 @@
       <c r="H534" t="inlineStr"/>
       <c r="I534" t="inlineStr"/>
       <c r="J534" t="inlineStr"/>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr"/>
       <c r="M534" t="inlineStr"/>
       <c r="N534" t="inlineStr">
@@ -31384,7 +33616,11 @@
       <c r="H535" t="inlineStr"/>
       <c r="I535" t="inlineStr"/>
       <c r="J535" t="inlineStr"/>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr"/>
       <c r="M535" t="inlineStr"/>
       <c r="N535" t="inlineStr">
@@ -31430,7 +33666,11 @@
       <c r="H536" t="inlineStr"/>
       <c r="I536" t="inlineStr"/>
       <c r="J536" t="inlineStr"/>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr"/>
       <c r="M536" t="inlineStr"/>
       <c r="N536" t="inlineStr">
@@ -31457,7 +33697,11 @@
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
-      <c r="D537" t="inlineStr"/>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E537" t="inlineStr"/>
       <c r="F537" t="inlineStr">
         <is>
@@ -31472,7 +33716,11 @@
       <c r="H537" t="inlineStr"/>
       <c r="I537" t="inlineStr"/>
       <c r="J537" t="inlineStr"/>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr"/>
       <c r="M537" t="inlineStr"/>
       <c r="N537" t="inlineStr">
@@ -31526,7 +33774,11 @@
       </c>
       <c r="I538" t="inlineStr"/>
       <c r="J538" t="inlineStr"/>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>TMPAPORTESDEVUELTOS_2</t>
@@ -31561,7 +33813,11 @@
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
-      <c r="D539" t="inlineStr"/>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E539" t="inlineStr"/>
       <c r="F539" t="inlineStr">
         <is>
@@ -31576,7 +33832,11 @@
       <c r="H539" t="inlineStr"/>
       <c r="I539" t="inlineStr"/>
       <c r="J539" t="inlineStr"/>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr"/>
       <c r="M539" t="inlineStr"/>
       <c r="N539" t="inlineStr">
@@ -31603,7 +33863,11 @@
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
-      <c r="D540" t="inlineStr"/>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E540" t="inlineStr"/>
       <c r="F540" t="inlineStr">
         <is>
@@ -31618,7 +33882,11 @@
       <c r="H540" t="inlineStr"/>
       <c r="I540" t="inlineStr"/>
       <c r="J540" t="inlineStr"/>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr"/>
       <c r="M540" t="inlineStr"/>
       <c r="N540" t="inlineStr">
@@ -31645,7 +33913,11 @@
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
-      <c r="D541" t="inlineStr"/>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E541" t="inlineStr"/>
       <c r="F541" t="inlineStr">
         <is>
@@ -31660,7 +33932,11 @@
       <c r="H541" t="inlineStr"/>
       <c r="I541" t="inlineStr"/>
       <c r="J541" t="inlineStr"/>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr"/>
       <c r="M541" t="inlineStr"/>
       <c r="N541" t="inlineStr">
@@ -31687,7 +33963,11 @@
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
-      <c r="D542" t="inlineStr"/>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E542" t="inlineStr"/>
       <c r="F542" t="inlineStr">
         <is>
@@ -31702,7 +33982,11 @@
       <c r="H542" t="inlineStr"/>
       <c r="I542" t="inlineStr"/>
       <c r="J542" t="inlineStr"/>
-      <c r="K542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L542" t="inlineStr"/>
       <c r="M542" t="inlineStr"/>
       <c r="N542" t="inlineStr">
@@ -31729,7 +34013,11 @@
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
-      <c r="D543" t="inlineStr"/>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E543" t="inlineStr"/>
       <c r="F543" t="inlineStr">
         <is>
@@ -31744,7 +34032,11 @@
       <c r="H543" t="inlineStr"/>
       <c r="I543" t="inlineStr"/>
       <c r="J543" t="inlineStr"/>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr"/>
       <c r="M543" t="inlineStr"/>
       <c r="N543" t="inlineStr">
@@ -31771,7 +34063,11 @@
         </is>
       </c>
       <c r="C544" t="inlineStr"/>
-      <c r="D544" t="inlineStr"/>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E544" t="inlineStr"/>
       <c r="F544" t="inlineStr">
         <is>
@@ -31786,7 +34082,11 @@
       <c r="H544" t="inlineStr"/>
       <c r="I544" t="inlineStr"/>
       <c r="J544" t="inlineStr"/>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr"/>
       <c r="M544" t="inlineStr"/>
       <c r="N544" t="inlineStr">
@@ -31813,7 +34113,11 @@
         </is>
       </c>
       <c r="C545" t="inlineStr"/>
-      <c r="D545" t="inlineStr"/>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E545" t="inlineStr"/>
       <c r="F545" t="inlineStr">
         <is>
@@ -31828,7 +34132,11 @@
       <c r="H545" t="inlineStr"/>
       <c r="I545" t="inlineStr"/>
       <c r="J545" t="inlineStr"/>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr"/>
       <c r="M545" t="inlineStr"/>
       <c r="N545" t="inlineStr">
@@ -31851,7 +34159,11 @@
         </is>
       </c>
       <c r="C546" t="inlineStr"/>
-      <c r="D546" t="inlineStr"/>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E546" t="inlineStr"/>
       <c r="F546" t="inlineStr">
         <is>
@@ -31866,7 +34178,11 @@
       <c r="H546" t="inlineStr"/>
       <c r="I546" t="inlineStr"/>
       <c r="J546" t="inlineStr"/>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr"/>
       <c r="M546" t="inlineStr"/>
       <c r="N546" t="inlineStr">
@@ -31893,7 +34209,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D547" t="inlineStr"/>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E547" t="inlineStr"/>
       <c r="F547" t="inlineStr">
         <is>
@@ -31908,7 +34228,11 @@
       <c r="H547" t="inlineStr"/>
       <c r="I547" t="inlineStr"/>
       <c r="J547" t="inlineStr"/>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr"/>
       <c r="M547" t="inlineStr"/>
       <c r="N547" t="inlineStr">
@@ -31935,7 +34259,11 @@
         </is>
       </c>
       <c r="C548" t="inlineStr"/>
-      <c r="D548" t="inlineStr"/>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E548" t="inlineStr"/>
       <c r="F548" t="inlineStr">
         <is>
@@ -31950,7 +34278,11 @@
       <c r="H548" t="inlineStr"/>
       <c r="I548" t="inlineStr"/>
       <c r="J548" t="inlineStr"/>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr"/>
       <c r="M548" t="inlineStr"/>
       <c r="N548" t="inlineStr">
@@ -31977,7 +34309,11 @@
         </is>
       </c>
       <c r="C549" t="inlineStr"/>
-      <c r="D549" t="inlineStr"/>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E549" t="inlineStr"/>
       <c r="F549" t="inlineStr">
         <is>
@@ -31992,7 +34328,11 @@
       <c r="H549" t="inlineStr"/>
       <c r="I549" t="inlineStr"/>
       <c r="J549" t="inlineStr"/>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr"/>
       <c r="M549" t="inlineStr"/>
       <c r="N549" t="inlineStr">
@@ -32019,7 +34359,11 @@
         </is>
       </c>
       <c r="C550" t="inlineStr"/>
-      <c r="D550" t="inlineStr"/>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E550" t="inlineStr"/>
       <c r="F550" t="inlineStr">
         <is>
@@ -32034,7 +34378,11 @@
       <c r="H550" t="inlineStr"/>
       <c r="I550" t="inlineStr"/>
       <c r="J550" t="inlineStr"/>
-      <c r="K550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L550" t="inlineStr"/>
       <c r="M550" t="inlineStr"/>
       <c r="N550" t="inlineStr">
@@ -32061,7 +34409,11 @@
         </is>
       </c>
       <c r="C551" t="inlineStr"/>
-      <c r="D551" t="inlineStr"/>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E551" t="inlineStr"/>
       <c r="F551" t="inlineStr">
         <is>
@@ -32076,7 +34428,11 @@
       <c r="H551" t="inlineStr"/>
       <c r="I551" t="inlineStr"/>
       <c r="J551" t="inlineStr"/>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr"/>
       <c r="M551" t="inlineStr"/>
       <c r="N551" t="inlineStr">
@@ -32103,7 +34459,11 @@
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
-      <c r="D552" t="inlineStr"/>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E552" t="inlineStr"/>
       <c r="F552" t="inlineStr">
         <is>
@@ -32118,7 +34478,11 @@
       <c r="H552" t="inlineStr"/>
       <c r="I552" t="inlineStr"/>
       <c r="J552" t="inlineStr"/>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr"/>
       <c r="M552" t="inlineStr"/>
       <c r="N552" t="inlineStr">
@@ -32145,7 +34509,11 @@
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
-      <c r="D553" t="inlineStr"/>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E553" t="inlineStr"/>
       <c r="F553" t="inlineStr">
         <is>
@@ -32160,7 +34528,11 @@
       <c r="H553" t="inlineStr"/>
       <c r="I553" t="inlineStr"/>
       <c r="J553" t="inlineStr"/>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr"/>
       <c r="M553" t="inlineStr"/>
       <c r="N553" t="inlineStr">
@@ -32187,7 +34559,11 @@
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
-      <c r="D554" t="inlineStr"/>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E554" t="inlineStr"/>
       <c r="F554" t="inlineStr">
         <is>
@@ -32202,7 +34578,11 @@
       <c r="H554" t="inlineStr"/>
       <c r="I554" t="inlineStr"/>
       <c r="J554" t="inlineStr"/>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr"/>
       <c r="M554" t="inlineStr"/>
       <c r="N554" t="inlineStr">
@@ -32229,7 +34609,11 @@
         </is>
       </c>
       <c r="C555" t="inlineStr"/>
-      <c r="D555" t="inlineStr"/>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E555" t="inlineStr"/>
       <c r="F555" t="inlineStr">
         <is>
@@ -32244,7 +34628,11 @@
       <c r="H555" t="inlineStr"/>
       <c r="I555" t="inlineStr"/>
       <c r="J555" t="inlineStr"/>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr"/>
       <c r="M555" t="inlineStr"/>
       <c r="N555" t="inlineStr">
@@ -32275,7 +34663,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D556" t="inlineStr"/>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E556" t="inlineStr"/>
       <c r="F556" t="inlineStr">
         <is>
@@ -32290,7 +34682,11 @@
       <c r="H556" t="inlineStr"/>
       <c r="I556" t="inlineStr"/>
       <c r="J556" t="inlineStr"/>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr"/>
       <c r="M556" t="inlineStr"/>
       <c r="N556" t="inlineStr">
@@ -32321,7 +34717,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D557" t="inlineStr"/>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E557" t="inlineStr"/>
       <c r="F557" t="inlineStr">
         <is>
@@ -32336,7 +34736,11 @@
       <c r="H557" t="inlineStr"/>
       <c r="I557" t="inlineStr"/>
       <c r="J557" t="inlineStr"/>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr"/>
       <c r="M557" t="inlineStr"/>
       <c r="N557" t="inlineStr">
@@ -32367,7 +34771,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D558" t="inlineStr"/>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E558" t="inlineStr"/>
       <c r="F558" t="inlineStr">
         <is>
@@ -32382,7 +34790,11 @@
       <c r="H558" t="inlineStr"/>
       <c r="I558" t="inlineStr"/>
       <c r="J558" t="inlineStr"/>
-      <c r="K558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr"/>
       <c r="M558" t="inlineStr"/>
       <c r="N558" t="inlineStr">
@@ -32413,7 +34825,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D559" t="inlineStr"/>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E559" t="inlineStr"/>
       <c r="F559" t="inlineStr">
         <is>
@@ -32428,7 +34844,11 @@
       <c r="H559" t="inlineStr"/>
       <c r="I559" t="inlineStr"/>
       <c r="J559" t="inlineStr"/>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr"/>
       <c r="M559" t="inlineStr"/>
       <c r="N559" t="inlineStr">
@@ -32459,7 +34879,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D560" t="inlineStr"/>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E560" t="inlineStr"/>
       <c r="F560" t="inlineStr">
         <is>
@@ -32474,7 +34898,11 @@
       <c r="H560" t="inlineStr"/>
       <c r="I560" t="inlineStr"/>
       <c r="J560" t="inlineStr"/>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr"/>
       <c r="M560" t="inlineStr"/>
       <c r="N560" t="inlineStr">
@@ -32505,7 +34933,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D561" t="inlineStr"/>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E561" t="inlineStr"/>
       <c r="F561" t="inlineStr">
         <is>
@@ -32520,7 +34952,11 @@
       <c r="H561" t="inlineStr"/>
       <c r="I561" t="inlineStr"/>
       <c r="J561" t="inlineStr"/>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr"/>
       <c r="M561" t="inlineStr"/>
       <c r="N561" t="inlineStr">
@@ -32578,7 +35014,11 @@
       </c>
       <c r="I562" t="inlineStr"/>
       <c r="J562" t="inlineStr"/>
-      <c r="K562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr">
         <is>
           <t>TMP_EMPL_IRRE_0002</t>
@@ -32613,7 +35053,11 @@
         </is>
       </c>
       <c r="C563" t="inlineStr"/>
-      <c r="D563" t="inlineStr"/>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E563" t="inlineStr"/>
       <c r="F563" t="inlineStr">
         <is>
@@ -32628,7 +35072,11 @@
       <c r="H563" t="inlineStr"/>
       <c r="I563" t="inlineStr"/>
       <c r="J563" t="inlineStr"/>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr"/>
       <c r="M563" t="inlineStr"/>
       <c r="N563" t="inlineStr">
@@ -32655,7 +35103,11 @@
         </is>
       </c>
       <c r="C564" t="inlineStr"/>
-      <c r="D564" t="inlineStr"/>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E564" t="inlineStr"/>
       <c r="F564" t="inlineStr">
         <is>
@@ -32670,7 +35122,11 @@
       <c r="H564" t="inlineStr"/>
       <c r="I564" t="inlineStr"/>
       <c r="J564" t="inlineStr"/>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr"/>
       <c r="M564" t="inlineStr"/>
       <c r="N564" t="inlineStr">
@@ -32693,7 +35149,11 @@
         </is>
       </c>
       <c r="C565" t="inlineStr"/>
-      <c r="D565" t="inlineStr"/>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E565" t="inlineStr"/>
       <c r="F565" t="inlineStr">
         <is>
@@ -32708,7 +35168,11 @@
       <c r="H565" t="inlineStr"/>
       <c r="I565" t="inlineStr"/>
       <c r="J565" t="inlineStr"/>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr"/>
       <c r="M565" t="inlineStr"/>
       <c r="N565" t="inlineStr">
@@ -32731,7 +35195,11 @@
         </is>
       </c>
       <c r="C566" t="inlineStr"/>
-      <c r="D566" t="inlineStr"/>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E566" t="inlineStr"/>
       <c r="F566" t="inlineStr">
         <is>
@@ -32746,7 +35214,11 @@
       <c r="H566" t="inlineStr"/>
       <c r="I566" t="inlineStr"/>
       <c r="J566" t="inlineStr"/>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr"/>
       <c r="M566" t="inlineStr"/>
       <c r="N566" t="inlineStr">
@@ -32769,7 +35241,11 @@
         </is>
       </c>
       <c r="C567" t="inlineStr"/>
-      <c r="D567" t="inlineStr"/>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E567" t="inlineStr"/>
       <c r="F567" t="inlineStr">
         <is>
@@ -32784,7 +35260,11 @@
       <c r="H567" t="inlineStr"/>
       <c r="I567" t="inlineStr"/>
       <c r="J567" t="inlineStr"/>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr"/>
       <c r="M567" t="inlineStr"/>
       <c r="N567" t="inlineStr">
@@ -32811,7 +35291,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D568" t="inlineStr"/>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E568" t="inlineStr"/>
       <c r="F568" t="inlineStr">
         <is>
@@ -32826,7 +35310,11 @@
       <c r="H568" t="inlineStr"/>
       <c r="I568" t="inlineStr"/>
       <c r="J568" t="inlineStr"/>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr"/>
       <c r="M568" t="inlineStr"/>
       <c r="N568" t="inlineStr"/>
@@ -32845,7 +35333,11 @@
         </is>
       </c>
       <c r="C569" t="inlineStr"/>
-      <c r="D569" t="inlineStr"/>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E569" t="inlineStr"/>
       <c r="F569" t="inlineStr">
         <is>
@@ -32860,7 +35352,11 @@
       <c r="H569" t="inlineStr"/>
       <c r="I569" t="inlineStr"/>
       <c r="J569" t="inlineStr"/>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr"/>
       <c r="M569" t="inlineStr"/>
       <c r="N569" t="inlineStr">
@@ -32887,7 +35383,11 @@
         </is>
       </c>
       <c r="C570" t="inlineStr"/>
-      <c r="D570" t="inlineStr"/>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E570" t="inlineStr"/>
       <c r="F570" t="inlineStr">
         <is>
@@ -32902,7 +35402,11 @@
       <c r="H570" t="inlineStr"/>
       <c r="I570" t="inlineStr"/>
       <c r="J570" t="inlineStr"/>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr"/>
       <c r="M570" t="inlineStr"/>
       <c r="N570" t="inlineStr">
@@ -32929,7 +35433,11 @@
         </is>
       </c>
       <c r="C571" t="inlineStr"/>
-      <c r="D571" t="inlineStr"/>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E571" t="inlineStr"/>
       <c r="F571" t="inlineStr">
         <is>
@@ -32944,7 +35452,11 @@
       <c r="H571" t="inlineStr"/>
       <c r="I571" t="inlineStr"/>
       <c r="J571" t="inlineStr"/>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr"/>
       <c r="M571" t="inlineStr"/>
       <c r="N571" t="inlineStr">
@@ -32971,7 +35483,11 @@
         </is>
       </c>
       <c r="C572" t="inlineStr"/>
-      <c r="D572" t="inlineStr"/>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E572" t="inlineStr"/>
       <c r="F572" t="inlineStr">
         <is>
@@ -32986,7 +35502,11 @@
       <c r="H572" t="inlineStr"/>
       <c r="I572" t="inlineStr"/>
       <c r="J572" t="inlineStr"/>
-      <c r="K572" t="inlineStr"/>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L572" t="inlineStr"/>
       <c r="M572" t="inlineStr"/>
       <c r="N572" t="inlineStr">
@@ -33013,7 +35533,11 @@
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
-      <c r="D573" t="inlineStr"/>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E573" t="inlineStr"/>
       <c r="F573" t="inlineStr">
         <is>
@@ -33028,7 +35552,11 @@
       <c r="H573" t="inlineStr"/>
       <c r="I573" t="inlineStr"/>
       <c r="J573" t="inlineStr"/>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr"/>
       <c r="M573" t="inlineStr"/>
       <c r="N573" t="inlineStr">
@@ -33055,7 +35583,11 @@
         </is>
       </c>
       <c r="C574" t="inlineStr"/>
-      <c r="D574" t="inlineStr"/>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E574" t="inlineStr"/>
       <c r="F574" t="inlineStr">
         <is>
@@ -33070,7 +35602,11 @@
       <c r="H574" t="inlineStr"/>
       <c r="I574" t="inlineStr"/>
       <c r="J574" t="inlineStr"/>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr"/>
       <c r="M574" t="inlineStr"/>
       <c r="N574" t="inlineStr">
@@ -33097,7 +35633,11 @@
         </is>
       </c>
       <c r="C575" t="inlineStr"/>
-      <c r="D575" t="inlineStr"/>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E575" t="inlineStr"/>
       <c r="F575" t="inlineStr">
         <is>
@@ -33112,7 +35652,11 @@
       <c r="H575" t="inlineStr"/>
       <c r="I575" t="inlineStr"/>
       <c r="J575" t="inlineStr"/>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr"/>
       <c r="M575" t="inlineStr"/>
       <c r="N575" t="inlineStr">
@@ -33139,7 +35683,11 @@
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
-      <c r="D576" t="inlineStr"/>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E576" t="inlineStr"/>
       <c r="F576" t="inlineStr">
         <is>
@@ -33154,7 +35702,11 @@
       <c r="H576" t="inlineStr"/>
       <c r="I576" t="inlineStr"/>
       <c r="J576" t="inlineStr"/>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr"/>
       <c r="M576" t="inlineStr"/>
       <c r="N576" t="inlineStr">
@@ -33185,7 +35737,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D577" t="inlineStr"/>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E577" t="inlineStr"/>
       <c r="F577" t="inlineStr">
         <is>
@@ -33200,7 +35756,11 @@
       <c r="H577" t="inlineStr"/>
       <c r="I577" t="inlineStr"/>
       <c r="J577" t="inlineStr"/>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr"/>
       <c r="M577" t="inlineStr"/>
       <c r="N577" t="inlineStr">
@@ -33227,7 +35787,11 @@
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
-      <c r="D578" t="inlineStr"/>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E578" t="inlineStr"/>
       <c r="F578" t="inlineStr">
         <is>
@@ -33242,7 +35806,11 @@
       <c r="H578" t="inlineStr"/>
       <c r="I578" t="inlineStr"/>
       <c r="J578" t="inlineStr"/>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr"/>
       <c r="M578" t="inlineStr"/>
       <c r="N578" t="inlineStr">
@@ -33300,7 +35868,11 @@
       </c>
       <c r="I579" t="inlineStr"/>
       <c r="J579" t="inlineStr"/>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr">
         <is>
           <t>aux_resm_aprt_ins2</t>
@@ -33335,7 +35907,11 @@
         </is>
       </c>
       <c r="C580" t="inlineStr"/>
-      <c r="D580" t="inlineStr"/>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E580" t="inlineStr"/>
       <c r="F580" t="inlineStr">
         <is>
@@ -33350,7 +35926,11 @@
       <c r="H580" t="inlineStr"/>
       <c r="I580" t="inlineStr"/>
       <c r="J580" t="inlineStr"/>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr"/>
       <c r="M580" t="inlineStr"/>
       <c r="N580" t="inlineStr">
@@ -33377,7 +35957,11 @@
         </is>
       </c>
       <c r="C581" t="inlineStr"/>
-      <c r="D581" t="inlineStr"/>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E581" t="inlineStr"/>
       <c r="F581" t="inlineStr">
         <is>
@@ -33392,7 +35976,11 @@
       <c r="H581" t="inlineStr"/>
       <c r="I581" t="inlineStr"/>
       <c r="J581" t="inlineStr"/>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr"/>
       <c r="M581" t="inlineStr"/>
       <c r="N581" t="inlineStr">
@@ -33423,7 +36011,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D582" t="inlineStr"/>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E582" t="inlineStr"/>
       <c r="F582" t="inlineStr">
         <is>
@@ -33442,7 +36034,11 @@
       </c>
       <c r="I582" t="inlineStr"/>
       <c r="J582" t="inlineStr"/>
-      <c r="K582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L582" t="inlineStr">
         <is>
           <t>DET_DOCU_DGTL</t>
@@ -33481,7 +36077,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D583" t="inlineStr"/>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E583" t="inlineStr"/>
       <c r="F583" t="inlineStr">
         <is>
@@ -33500,7 +36100,11 @@
       </c>
       <c r="I583" t="inlineStr"/>
       <c r="J583" t="inlineStr"/>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>DET_DOCU_DGTL</t>
@@ -33539,7 +36143,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D584" t="inlineStr"/>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E584" t="inlineStr"/>
       <c r="F584" t="inlineStr">
         <is>
@@ -33558,7 +36166,11 @@
       </c>
       <c r="I584" t="inlineStr"/>
       <c r="J584" t="inlineStr"/>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>DET_DOCU_DGTL</t>
@@ -33593,7 +36205,11 @@
         </is>
       </c>
       <c r="C585" t="inlineStr"/>
-      <c r="D585" t="inlineStr"/>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E585" t="inlineStr"/>
       <c r="F585" t="inlineStr">
         <is>
@@ -33608,7 +36224,11 @@
       <c r="H585" t="inlineStr"/>
       <c r="I585" t="inlineStr"/>
       <c r="J585" t="inlineStr"/>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr"/>
       <c r="M585" t="inlineStr"/>
       <c r="N585" t="inlineStr">
@@ -33639,7 +36259,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D586" t="inlineStr"/>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E586" t="inlineStr"/>
       <c r="F586" t="inlineStr">
         <is>
@@ -33654,7 +36278,11 @@
       <c r="H586" t="inlineStr"/>
       <c r="I586" t="inlineStr"/>
       <c r="J586" t="inlineStr"/>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr"/>
       <c r="M586" t="inlineStr"/>
       <c r="N586" t="inlineStr">
@@ -33685,7 +36313,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D587" t="inlineStr"/>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E587" t="inlineStr"/>
       <c r="F587" t="inlineStr">
         <is>
@@ -33700,7 +36332,11 @@
       <c r="H587" t="inlineStr"/>
       <c r="I587" t="inlineStr"/>
       <c r="J587" t="inlineStr"/>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr"/>
       <c r="M587" t="inlineStr"/>
       <c r="N587" t="inlineStr">
@@ -33731,7 +36367,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D588" t="inlineStr"/>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E588" t="inlineStr"/>
       <c r="F588" t="inlineStr">
         <is>
@@ -33746,7 +36386,11 @@
       <c r="H588" t="inlineStr"/>
       <c r="I588" t="inlineStr"/>
       <c r="J588" t="inlineStr"/>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr"/>
       <c r="M588" t="inlineStr"/>
       <c r="N588" t="inlineStr">
@@ -33777,7 +36421,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D589" t="inlineStr"/>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E589" t="inlineStr"/>
       <c r="F589" t="inlineStr">
         <is>
@@ -33792,7 +36440,11 @@
       <c r="H589" t="inlineStr"/>
       <c r="I589" t="inlineStr"/>
       <c r="J589" t="inlineStr"/>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr"/>
       <c r="M589" t="inlineStr"/>
       <c r="N589" t="inlineStr">
@@ -33819,7 +36471,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D590" t="inlineStr"/>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E590" t="inlineStr"/>
       <c r="F590" t="inlineStr">
         <is>
@@ -33834,7 +36490,11 @@
       <c r="H590" t="inlineStr"/>
       <c r="I590" t="inlineStr"/>
       <c r="J590" t="inlineStr"/>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr"/>
       <c r="M590" t="inlineStr"/>
       <c r="N590" t="inlineStr">
@@ -33861,7 +36521,11 @@
           <t>Oracle</t>
         </is>
       </c>
-      <c r="D591" t="inlineStr"/>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>(destino parametrizado — pendiente)</t>
+        </is>
+      </c>
       <c r="E591" t="inlineStr"/>
       <c r="F591" t="inlineStr">
         <is>
@@ -33876,7 +36540,11 @@
       <c r="H591" t="inlineStr"/>
       <c r="I591" t="inlineStr"/>
       <c r="J591" t="inlineStr"/>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr"/>
       <c r="M591" t="inlineStr"/>
       <c r="N591" t="inlineStr">

--- a/client/public/artefactos/ADI-05.xlsx
+++ b/client/public/artefactos/ADI-05.xlsx
@@ -3645,7 +3645,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>cadena_pru_gtw</t>
+          <t>INFORMIX</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>cadena_pru_gtw</t>
+          <t>INFORMIX</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>cadena_pru_gtw</t>
+          <t>INFORMIX</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>cadena_pru_gtw</t>
+          <t>INFORMIX</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
